--- a/corr/correlation.xlsx
+++ b/corr/correlation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV48"/>
+  <dimension ref="A1:BC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,13 @@
     <col width="12" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,6 +710,41 @@
           <t>SalePrice</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -714,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1007388097059316</v>
+        <v>0.2620118831010028</v>
       </c>
       <c r="D2" t="n">
         <v>0.1132939619346847</v>
@@ -726,7 +768,7 @@
         <v>-0.05345696235809445</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1050098329680274</v>
+        <v>0.04757662378637828</v>
       </c>
       <c r="H2" t="n">
         <v>0.127864400787588</v>
@@ -744,34 +786,34 @@
         <v>0.07092114882812249</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07666999700757246</v>
+        <v>-0.03483742689135604</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.00931230949382297</v>
+        <v>-0.02031697272406424</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1608292768227431</v>
+        <v>0.113029208237141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2382736686968275</v>
+        <v>0.07816263674239077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2451809314438915</v>
+        <v>0.2320571783242125</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04254924407230871</v>
+        <v>-0.008962386564844183</v>
       </c>
       <c r="S2" t="n">
-        <v>0.04998143020178656</v>
+        <v>0.03613648099968293</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2203472317221379</v>
+        <v>0.1947769519356069</v>
       </c>
       <c r="U2" t="n">
         <v>0.01051433344513178</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.02785565775913115</v>
+        <v>-0.02739783085222267</v>
       </c>
       <c r="W2" t="n">
         <v>0.1205478702383639</v>
@@ -783,7 +825,7 @@
         <v>0.1444936461070019</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03442465807394676</v>
+        <v>0.03569160228646356</v>
       </c>
       <c r="AA2" t="n">
         <v>0.1274777934821109</v>
@@ -813,28 +855,28 @@
         <v>0.01304726087886099</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.01677975886666707</v>
+        <v>-0.01055853844824409</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.06960495214754152</v>
+        <v>0.07439822098927829</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02736610487444278</v>
+        <v>0.006146912610430093</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0234987244183133</v>
+        <v>0.0143966997370734</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02296873201099656</v>
+        <v>0.01832593015222203</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1141063586023839</v>
+        <v>0.1333509268377824</v>
       </c>
       <c r="AP2" t="n">
         <v>0.1517547790015385</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.05960573010301279</v>
+        <v>-0.04188524611986889</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.03732683663916023</v>
@@ -849,7 +891,28 @@
         <v>-0.01209396018343283</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.209623944799484</v>
+        <v>0.1793031336837223</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.227365919677957</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.08312430396308478</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.01661150843605789</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.04927282497289349</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.2042643389660964</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.1979126567360726</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.1090601958665024</v>
       </c>
     </row>
     <row r="3">
@@ -859,145 +922,166 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1007388097059316</v>
+        <v>0.2620118831010028</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3154840370105772</v>
+        <v>-0.360961007599488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1058057417549641</v>
+        <v>0.1782200461398294</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.005636270274099272</v>
+        <v>-0.006307665348357836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1033205056304603</v>
+        <v>0.06926211310172734</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05557005342864099</v>
+        <v>0.1033576066076336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01473197162046976</v>
+        <v>0.03840199786060628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07233553751949937</v>
+        <v>0.08170958860881711</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03134918682097262</v>
+        <v>0.02688312903609127</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2288299588752998</v>
+        <v>0.2121473794095162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2141031307055767</v>
+        <v>0.09696623585067322</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1111697454962486</v>
+        <v>0.08431162283892255</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.002618359950095396</v>
+        <v>0.04751026295016244</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2608331345451577</v>
+        <v>0.1255251210981429</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2994745785077633</v>
+        <v>0.4674421914748393</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05098594829349382</v>
+        <v>-0.01277519729151235</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004778969866349541</v>
+        <v>-0.01068106422476788</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2631161671671479</v>
+        <v>0.3854565955200016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1581545310600149</v>
+        <v>0.1382790698463231</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0480455708882969</v>
+        <v>0.04789604308002807</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1260306265196436</v>
+        <v>0.1791926429023915</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01425946856643189</v>
+        <v>0.03872837510970988</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1196899081513157</v>
+        <v>0.279172712322895</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.01778387050484175</v>
+        <v>0.002947235479246431</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06786351851282853</v>
+        <v>0.1184997355344485</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1900147776254092</v>
+        <v>0.3601314045179373</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2713640096245423</v>
+        <v>0.3277648971412582</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.185332150761069</v>
+        <v>0.2755531461584911</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1247560997887132</v>
+        <v>0.1908356310209044</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1548707397535409</v>
+        <v>0.2720103419891267</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1804027551511163</v>
+        <v>0.3220483813817084</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.07931311436416157</v>
+        <v>0.1459727480380153</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0760971750740833</v>
+        <v>0.137060669163895</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1716976872571128</v>
+        <v>0.1229153708307461</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08477380884021633</v>
+        <v>0.1377543698927563</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.01833973367221233</v>
+        <v>-0.01518603291759209</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.02042282958613336</v>
+        <v>0.0553752032449656</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.04316037769525196</v>
+        <v>0.08751837576497702</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0776723918801745</v>
+        <v>0.09725733278091506</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.09138095017275082</v>
+        <v>0.100574319100636</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.03806769201918332</v>
+        <v>0.08029769918252747</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.01483155851922715</v>
+        <v>-0.02310161380799476</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.01461138554969105</v>
+        <v>-0.02933197518168441</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.04305848750416469</v>
+        <v>0.05520830484444315</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.01426140729853185</v>
+        <v>-0.02716361470761305</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2638433538714056</v>
+        <v>0.3999231830717292</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.4268482779066</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.2363267252924848</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.1423863972652866</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.1921779906530965</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.7642429805733403</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.3253484859825745</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.1413963340059529</v>
       </c>
     </row>
     <row r="4">
@@ -1010,7 +1094,7 @@
         <v>0.1132939619346847</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3154840370105772</v>
+        <v>-0.360961007599488</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1022,7 +1106,7 @@
         <v>0.03374664227524166</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.08979965135104412</v>
+        <v>-0.05816012455287201</v>
       </c>
       <c r="H4" t="n">
         <v>-0.188667599072124</v>
@@ -1040,34 +1124,34 @@
         <v>-0.1835399288009137</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.157718009246914</v>
+        <v>-0.08539681732462175</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06041945162979315</v>
+        <v>-0.04541982085985333</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0141788984367829</v>
+        <v>-0.03210331166482896</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2004691684539251</v>
+        <v>-0.1174363192084952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.189251413035684</v>
+        <v>-0.1783322490714215</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.08937970396442449</v>
+        <v>-0.02594566140072222</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007972512584302132</v>
+        <v>0.0223161067069179</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2127413571582553</v>
+        <v>-0.2017758480876663</v>
       </c>
       <c r="U4" t="n">
         <v>-0.06463838278416811</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.05772902957154372</v>
+        <v>-0.05837331008026488</v>
       </c>
       <c r="W4" t="n">
         <v>-0.1842126487010587</v>
@@ -1079,7 +1163,7 @@
         <v>-0.06002756363845823</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09486962103415594</v>
+        <v>0.09592264877022069</v>
       </c>
       <c r="AA4" t="n">
         <v>-0.1579333480504451</v>
@@ -1109,28 +1193,28 @@
         <v>-0.1028635742197958</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1617167981801607</v>
+        <v>-0.1552034491984531</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.09313478427436463</v>
+        <v>-0.1420349890359973</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09509194788899258</v>
+        <v>0.1173664779032643</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.03380096584269817</v>
+        <v>-0.03249336311759071</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.06518217240407964</v>
+        <v>-0.05794917056905853</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.04710024174230158</v>
+        <v>-0.05251125911772074</v>
       </c>
       <c r="AP4" t="n">
         <v>-0.05332093096219565</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.02863767848728298</v>
+        <v>-0.01868136474241074</v>
       </c>
       <c r="AR4" t="n">
         <v>0.2306483290843977</v>
@@ -1145,7 +1229,28 @@
         <v>0.03739136080811351</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.2677593139178234</v>
+        <v>-0.2860016695949006</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.2289060345732974</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2180177782976908</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.1113689909139462</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.1760156841180942</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.2115348723672874</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.2194844033140831</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.1403310488050334</v>
       </c>
     </row>
     <row r="5">
@@ -1158,7 +1263,7 @@
         <v>0.1765610223501436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1058057417549641</v>
+        <v>0.1782200461398294</v>
       </c>
       <c r="D5" t="n">
         <v>-0.1989937681648747</v>
@@ -1170,7 +1275,7 @@
         <v>-0.09193234263907182</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4072521235240133</v>
+        <v>0.4093174936207199</v>
       </c>
       <c r="H5" t="n">
         <v>0.7262784907641405</v>
@@ -1188,34 +1293,34 @@
         <v>0.2965168412331978</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2396659661788912</v>
+        <v>0.05419924178436986</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05911869267068982</v>
+        <v>-0.1014691029011309</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3081589269056427</v>
+        <v>0.2684455626205436</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5378084986123908</v>
+        <v>0.3443687376885914</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4762238290781774</v>
+        <v>0.4560663293079087</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2954928791997097</v>
+        <v>0.1980644967825403</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.03042928397960513</v>
+        <v>-0.02992412300406221</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5930074300286527</v>
+        <v>0.614207376935223</v>
       </c>
       <c r="U5" t="n">
         <v>0.1110977861423025</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0401501576699883</v>
+        <v>-0.04156678956230443</v>
       </c>
       <c r="W5" t="n">
         <v>0.5505997093682546</v>
@@ -1227,7 +1332,7 @@
         <v>0.1016763562417855</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.183882234549221</v>
+        <v>-0.181779716663709</v>
       </c>
       <c r="AA5" t="n">
         <v>0.6733307811877888</v>
@@ -1257,28 +1362,28 @@
         <v>0.2869550382941626</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2389233922491861</v>
+        <v>0.2832556297578568</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3088188233594516</v>
+        <v>0.4451009458903159</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.1139368585956817</v>
+        <v>-0.1586481247560412</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03037056713526447</v>
+        <v>0.02754596598754004</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0648863604935155</v>
+        <v>0.04998336722916914</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.06516584360589192</v>
+        <v>0.07265056252291785</v>
       </c>
       <c r="AP5" t="n">
         <v>0.08527788688766683</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.03140621050074643</v>
+        <v>-0.08513084299391066</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.5726294680112988</v>
@@ -1293,7 +1398,28 @@
         <v>-0.02734670832780733</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.7909816005838053</v>
+        <v>0.8171846144867677</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.6761087278185191</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.5410628268191986</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.3528619144563227</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.5108040156227085</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.1631570870208681</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.8538092432026669</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.7562289347520853</v>
       </c>
     </row>
     <row r="6">
@@ -1306,7 +1432,7 @@
         <v>-0.05345696235809445</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.005636270274099272</v>
+        <v>-0.006307665348357836</v>
       </c>
       <c r="D6" t="n">
         <v>0.03374664227524166</v>
@@ -1318,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1256936336195367</v>
+        <v>-0.1543072144104304</v>
       </c>
       <c r="H6" t="n">
         <v>-0.1389422549081044</v>
@@ -1336,34 +1462,34 @@
         <v>-0.0567315016976149</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04623085591822497</v>
+        <v>0.04519965605268379</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04022916989976748</v>
+        <v>0.07799163320206677</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1368405698935223</v>
+        <v>-0.03080502229483537</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1710975146249219</v>
+        <v>0.008809942006818006</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1442027840490593</v>
+        <v>-0.1367913244540082</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02894211596581697</v>
+        <v>0.05593418424519243</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02549431991421348</v>
+        <v>0.02857982179631793</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07968586538833805</v>
+        <v>-0.1019595664820341</v>
       </c>
       <c r="U6" t="n">
         <v>-0.05494151543295182</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1178209150813927</v>
+        <v>0.1211699892540699</v>
       </c>
       <c r="W6" t="n">
         <v>-0.1941494887493022</v>
@@ -1375,7 +1501,7 @@
         <v>0.01298006009455062</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0870008554363805</v>
+        <v>-0.08499358392920293</v>
       </c>
       <c r="AA6" t="n">
         <v>-0.02670668967363533</v>
@@ -1405,28 +1531,28 @@
         <v>0.0167061861314389</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.003333699289385612</v>
+        <v>-0.03908477859755016</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.03258881352158505</v>
+        <v>-0.1007830116005938</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.07035618448230378</v>
+        <v>0.09247081485534324</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.02550366002413216</v>
+        <v>0.03883468262556374</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.05481052878611519</v>
+        <v>0.06154770796263515</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001984942268184163</v>
+        <v>-0.008085053397001643</v>
       </c>
       <c r="AP6" t="n">
         <v>-0.0148851152876456</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.06877680605724999</v>
+        <v>0.0792514540096167</v>
       </c>
       <c r="AR6" t="n">
         <v>0.3773254975104511</v>
@@ -1441,7 +1567,28 @@
         <v>0.04394974569248088</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.07785589404867797</v>
+        <v>-0.03686845383480093</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.135366689411354</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1740323190474399</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.01456751283012944</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.1010456772886713</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.06410178871052526</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.08379329820060734</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.58201439220482</v>
       </c>
     </row>
     <row r="7">
@@ -1451,145 +1598,166 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1050098329680274</v>
+        <v>0.04757662378637828</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1033205056304603</v>
+        <v>0.06926211310172734</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08979965135104412</v>
+        <v>-0.05816012455287201</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4072521235240133</v>
+        <v>0.4093174936207199</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1256936336195367</v>
+        <v>-0.1543072144104304</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3453291145773131</v>
+        <v>0.3516615672004296</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01806544599618654</v>
+        <v>-0.03832326907045634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2774899657791213</v>
+        <v>0.3005995349993343</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07320976503564644</v>
+        <v>0.1042538071763783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1751109274846845</v>
+        <v>0.18986071762954</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2612560549131624</v>
+        <v>0.1853676027424221</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07132962764448499</v>
+        <v>-0.06134501559716155</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1138621630816125</v>
+        <v>0.0923016287584893</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3600673680536377</v>
+        <v>0.1848371590970442</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3398504136832511</v>
+        <v>0.3272795044492487</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1738000004355764</v>
+        <v>-0.01459624485122176</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06862797990733829</v>
+        <v>-0.107795805322077</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3880520522217603</v>
+        <v>0.3023854049778036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08301004780135807</v>
+        <v>0.1132002623642533</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02740266233346421</v>
+        <v>0.04003930440607066</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2729988557264337</v>
+        <v>0.2763830153638608</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1991075194121956</v>
+        <v>0.1499277168145839</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.102774516136891</v>
+        <v>0.09038345551871309</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03845011208085553</v>
+        <v>-0.061518442784117</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2826198480701212</v>
+        <v>0.2952402610447823</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2795678875257759</v>
+        <v>0.2332534120233238</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2470152773621434</v>
+        <v>0.2242629866920038</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.274949821510542</v>
+        <v>0.2525214140819323</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2759213444756037</v>
+        <v>0.3336023101645342</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.361944566177457</v>
+        <v>0.3871512411356073</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3708841528088984</v>
+        <v>0.3683963625021248</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1349470486962461</v>
+        <v>0.1836721198874053</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1337485063855376</v>
+        <v>0.1854581699229837</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1599905296183509</v>
+        <v>0.1631064118362469</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1225283318319018</v>
+        <v>0.2070234255588875</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.1099067972602167</v>
+        <v>-0.1856798514711146</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.01914378432951321</v>
+        <v>0.04753954345656658</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.06224771119321619</v>
+        <v>0.03865821401417698</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0119283940295965</v>
+        <v>0.005661698818330052</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01322812811560468</v>
+        <v>-0.01331000024092372</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.02951224865746651</v>
+        <v>-0.05351138965223912</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.3114785424298824</v>
+        <v>-0.4070914822471848</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.1769905760956647</v>
+        <v>-0.2207990260776076</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.20476456477356</v>
+        <v>-0.2513446707483966</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.00831662258093285</v>
+        <v>-0.002286101713903709</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4726144990045736</v>
+        <v>0.4133179127442381</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.372667585004204</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.3230216242148177</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.1281951899989732</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.2204074039699015</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.1195047354117076</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.37859552916305</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.2328700160367897</v>
       </c>
     </row>
     <row r="8">
@@ -1602,7 +1770,7 @@
         <v>0.127864400787588</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05557005342864099</v>
+        <v>0.1033576066076336</v>
       </c>
       <c r="D8" t="n">
         <v>-0.188667599072124</v>
@@ -1614,7 +1782,7 @@
         <v>-0.1389422549081044</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3453291145773131</v>
+        <v>0.3516615672004296</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1632,34 +1800,34 @@
         <v>0.2491006251173818</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2037774999382381</v>
+        <v>0.03069575288241926</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07623624782346086</v>
+        <v>-0.1213789538748409</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2847047122866223</v>
+        <v>0.2256673891891761</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4705795564429219</v>
+        <v>0.2452917105714467</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3978353748610639</v>
+        <v>0.3738127494687071</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1795303237302894</v>
+        <v>0.09383680373166019</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06306156732584109</v>
+        <v>-0.05978742679099373</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4359860588448988</v>
+        <v>0.4451251178232018</v>
       </c>
       <c r="U8" t="n">
         <v>0.1245498087937538</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0562613370010995</v>
+        <v>-0.05770147302676296</v>
       </c>
       <c r="W8" t="n">
         <v>0.4839494160445375</v>
@@ -1671,7 +1839,7 @@
         <v>-0.01872859098087966</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.1512358721209085</v>
+        <v>-0.148587792628355</v>
       </c>
       <c r="AA8" t="n">
         <v>0.7161221955033013</v>
@@ -1701,28 +1869,28 @@
         <v>0.2146800450003872</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2079320871804168</v>
+        <v>0.2640730826792085</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2915531145011275</v>
+        <v>0.4256107287322423</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.1495888058226588</v>
+        <v>-0.1806157564489581</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.03693404140250921</v>
+        <v>0.04970139025731576</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0126882329502044</v>
+        <v>-0.003326157434690447</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.03476617239374453</v>
+        <v>0.03789537215966963</v>
       </c>
       <c r="AP8" t="n">
         <v>0.05543523010076364</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.03930981826985685</v>
+        <v>-0.07667236394458131</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.5975223201623887</v>
@@ -1737,7 +1905,28 @@
         <v>-0.006744813277590106</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.6826392416562586</v>
+        <v>0.6788402517304429</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.5167563883215376</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.4752771282643092</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.2831884714072568</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.3975409582261368</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.1393395701599008</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.6039132685475443</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.5018081658669395</v>
       </c>
     </row>
     <row r="9">
@@ -1750,7 +1939,7 @@
         <v>-0.04680701067762603</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01473197162046976</v>
+        <v>0.03840199786060628</v>
       </c>
       <c r="D9" t="n">
         <v>-0.01407320076142192</v>
@@ -1762,7 +1951,7 @@
         <v>0.3891631138997462</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.01806544599618654</v>
+        <v>-0.03832326907045634</v>
       </c>
       <c r="H9" t="n">
         <v>0.009183979533416028</v>
@@ -1780,34 +1969,34 @@
         <v>0.005712934216037774</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04091880895847957</v>
+        <v>0.08543402012102562</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06042891178150066</v>
+        <v>0.05877157472672545</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.07012820032438424</v>
+        <v>-0.02704443740013752</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.005871812953530698</v>
+        <v>0.06116115465050893</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.001391168173165931</v>
+        <v>0.006892828613742252</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02478221776872843</v>
+        <v>0.0176295976167304</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.03232520534395899</v>
+        <v>-0.0325788616546463</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01657261314789848</v>
+        <v>0.0009244218656472537</v>
       </c>
       <c r="U9" t="n">
         <v>0.03803233551425564</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09797365538453182</v>
+        <v>0.1002931551060214</v>
       </c>
       <c r="W9" t="n">
         <v>-0.003325472610971581</v>
@@ -1819,7 +2008,7 @@
         <v>0.01506473636648824</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.05034971149413901</v>
+        <v>-0.04943385772244818</v>
       </c>
       <c r="AA9" t="n">
         <v>0.05759177239223918</v>
@@ -1849,28 +2038,28 @@
         <v>0.1039399331634698</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.04687398599885621</v>
+        <v>0.02763431985015695</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0632802033987919</v>
+        <v>0.01778794828611252</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03509398209467423</v>
+        <v>0.03169632525125297</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.005196474953970466</v>
+        <v>0.01379328410463352</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.02859288412589658</v>
+        <v>0.01816380923242146</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.04438718368305009</v>
+        <v>0.04064725860066499</v>
       </c>
       <c r="AP9" t="n">
         <v>0.05178449846498944</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.05164863916650527</v>
+        <v>-0.005534917029517625</v>
       </c>
       <c r="AR9" t="n">
         <v>0.1041161887572947</v>
@@ -1885,7 +2074,28 @@
         <v>0.008053232838010438</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.01889911848241311</v>
+        <v>0.04931331923808516</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.01403754952097144</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.02685946190764365</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.06345874696087896</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.0004292104289614232</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.03894180634511635</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.01994354648091521</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.2671095005050831</v>
       </c>
     </row>
     <row r="10">
@@ -1898,7 +2108,7 @@
         <v>0.09271712468893432</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07233553751949937</v>
+        <v>0.08170958860881711</v>
       </c>
       <c r="D10" t="n">
         <v>-0.2115568210210603</v>
@@ -1910,7 +2120,7 @@
         <v>-0.1649964556546049</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2774899657791213</v>
+        <v>0.3005995349993343</v>
       </c>
       <c r="H10" t="n">
         <v>0.5655580939963543</v>
@@ -1928,34 +2138,34 @@
         <v>0.3993391165342395</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3046073540306732</v>
+        <v>0.2067498335422607</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.03099105033020036</v>
+        <v>-0.05499390668032467</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2571577182687437</v>
+        <v>0.3742596556830837</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5642987744292742</v>
+        <v>0.7118076889037235</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2935980146037869</v>
+        <v>0.2825622712322184</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1409869252557819</v>
+        <v>0.06674016007647685</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.05577487200473385</v>
+        <v>-0.06604675058278611</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3279556261553638</v>
+        <v>0.3427842114693724</v>
       </c>
       <c r="U10" t="n">
         <v>0.2234951821629657</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0133615596591872</v>
+        <v>-0.01639660104389544</v>
       </c>
       <c r="W10" t="n">
         <v>0.3712429593398341</v>
@@ -1967,7 +2177,7 @@
         <v>-0.03991267086986513</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.2777312041386026</v>
+        <v>-0.2782327713828404</v>
       </c>
       <c r="AA10" t="n">
         <v>0.5109380404168206</v>
@@ -1997,28 +2207,28 @@
         <v>0.1928051104976284</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2527025451603133</v>
+        <v>0.302954539549606</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.2539988660827411</v>
+        <v>0.3796758207222896</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.1815325757817224</v>
+        <v>-0.205747965457807</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.008096815232181972</v>
+        <v>0.00210532553658656</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.03439580927897198</v>
+        <v>0.02699806801220587</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02641484902600591</v>
+        <v>0.0287435892857033</v>
       </c>
       <c r="AP10" t="n">
         <v>0.0333716422403259</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.04440369387701099</v>
+        <v>-0.08799698280011924</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.6027976955326702</v>
@@ -2033,7 +2243,28 @@
         <v>-0.02146087298154877</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5852071991725194</v>
+        <v>0.6158037560867945</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.5666743097107507</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.4795322372170178</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.3212853189003391</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.3558553253172121</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.1221065087905358</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.5089738470469847</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.4055566283116501</v>
       </c>
     </row>
     <row r="11">
@@ -2046,7 +2277,7 @@
         <v>0.01533407616778145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03134918682097262</v>
+        <v>0.02688312903609127</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1082522052100353</v>
@@ -2058,7 +2289,7 @@
         <v>0.1323608044228719</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07320976503564644</v>
+        <v>0.1042538071763783</v>
       </c>
       <c r="H11" t="n">
         <v>0.1850458343525312</v>
@@ -2076,34 +2307,34 @@
         <v>0.2556874764827046</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1658013623196709</v>
+        <v>0.2349563074567287</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08190437346475933</v>
+        <v>0.09303490081690853</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1688210467379411</v>
+        <v>0.3869466398266659</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3725299684761661</v>
+        <v>0.8319494832933113</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0532167173495391</v>
+        <v>0.06517504291838358</v>
       </c>
       <c r="R11" t="n">
-        <v>0.05717705924973461</v>
+        <v>0.03807898552997514</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0336417249168556</v>
+        <v>-0.04397974208244301</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08353609322737154</v>
+        <v>0.09841980433192263</v>
       </c>
       <c r="U11" t="n">
         <v>0.1564646261042932</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06481138093656827</v>
+        <v>0.0634818533393815</v>
       </c>
       <c r="W11" t="n">
         <v>0.04209278017668745</v>
@@ -2115,7 +2346,7 @@
         <v>0.001995835976032751</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.2680236183359653</v>
+        <v>-0.2727126860482804</v>
       </c>
       <c r="AA11" t="n">
         <v>0.1825354417667602</v>
@@ -2145,28 +2376,28 @@
         <v>0.1446172768407943</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1241742761856272</v>
+        <v>0.1318166125841248</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.09670534790073362</v>
+        <v>0.144345252445279</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.04119538732054864</v>
+        <v>-0.03898723887817345</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.009149329224614857</v>
+        <v>-0.01387852719393275</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.03931131993286549</v>
+        <v>0.03676265871385045</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.008097674679767001</v>
+        <v>0.008180291844328594</v>
       </c>
       <c r="AP11" t="n">
         <v>0.00752055686231151</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.02324015718639813</v>
+        <v>-0.03534737041100905</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.1854754951310796</v>
@@ -2181,7 +2412,28 @@
         <v>-0.0602885069647519</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2126071564855786</v>
+        <v>0.274542739157557</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.3533567549098131</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.1857207163260521</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1969561437503825</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.1236750263299124</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.03940902129475717</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.2073599623356324</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.306451035316866</v>
       </c>
     </row>
     <row r="12">
@@ -2194,7 +2446,7 @@
         <v>0.07092114882812249</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2288299588752998</v>
+        <v>0.2121473794095162</v>
       </c>
       <c r="D12" t="n">
         <v>-0.1835399288009137</v>
@@ -2206,7 +2458,7 @@
         <v>-0.0567315016976149</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1751109274846845</v>
+        <v>0.18986071762954</v>
       </c>
       <c r="H12" t="n">
         <v>0.2491006251173818</v>
@@ -2224,34 +2476,34 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3691147912860215</v>
+        <v>0.2766156514470355</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09465818094043063</v>
+        <v>0.0615423838646779</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.03501253999458167</v>
+        <v>-0.03048739573037867</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3832911220850172</v>
+        <v>0.3222325728898507</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3048563489705075</v>
+        <v>0.2875432065743173</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.1065774427613611</v>
+        <v>-0.1653402840726587</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.05797476914950474</v>
+        <v>-0.06748835683957323</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1303773313455412</v>
+        <v>0.1130344944578868</v>
       </c>
       <c r="U12" t="n">
         <v>0.3386720768341057</v>
       </c>
       <c r="V12" t="n">
-        <v>0.078179947986335</v>
+        <v>0.07532148067412894</v>
       </c>
       <c r="W12" t="n">
         <v>0.09923253717822954</v>
@@ -2263,7 +2515,7 @@
         <v>-0.1158058397977214</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.121960616778857</v>
+        <v>-0.1258949459016662</v>
       </c>
       <c r="AA12" t="n">
         <v>0.2547068310561876</v>
@@ -2293,28 +2545,28 @@
         <v>0.07209979820896875</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2481288586557223</v>
+        <v>0.3156642176333909</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.08659009991280658</v>
+        <v>0.1203520939765843</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.09453206952634803</v>
+        <v>-0.1111821207154193</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.01585361683462282</v>
+        <v>-0.003342920658525988</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.04220682248103895</v>
+        <v>0.03790628162798328</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.04219029921216872</v>
+        <v>0.04259362651145121</v>
       </c>
       <c r="AP12" t="n">
         <v>0.0535813969539207</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.01728125661742881</v>
+        <v>-0.04052241369718979</v>
       </c>
       <c r="AR12" t="n">
         <v>-0.2919829814293874</v>
@@ -2329,7 +2581,28 @@
         <v>-0.06405975867337128</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.3746962210008858</v>
+        <v>0.3574213757606134</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.2775936811620962</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.2941108763826505</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.2093620057108942</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.1797252802398421</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.1094667207441255</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.1991739737769157</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.2048688576506116</v>
       </c>
     </row>
     <row r="13">
@@ -2339,145 +2612,166 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07666999700757246</v>
+        <v>-0.03483742689135604</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2141031307055767</v>
+        <v>0.09696623585067322</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.157718009246914</v>
+        <v>-0.08539681732462175</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2396659661788912</v>
+        <v>0.05419924178436986</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.04623085591822497</v>
+        <v>0.04519965605268379</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2612560549131624</v>
+        <v>0.1853676027424221</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2037774999382381</v>
+        <v>0.03069575288241926</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04091880895847957</v>
+        <v>0.08543402012102562</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3046073540306732</v>
+        <v>0.2067498335422607</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1658013623196709</v>
+        <v>0.2349563074567287</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3691147912860215</v>
+        <v>0.2766156514470355</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05011740004715102</v>
+        <v>0.1850511612061961</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4952514692570114</v>
+        <v>-0.2654875403797134</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5223960519923859</v>
+        <v>0.2901322106113485</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4458626560920056</v>
+        <v>0.1987339260441995</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1370789860800536</v>
+        <v>-0.2054256023359318</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06450259692146859</v>
+        <v>-0.06356301039149706</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2081711301453267</v>
+        <v>-0.01444038399297258</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6492117535742655</v>
+        <v>0.5911478882165804</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06741847791011704</v>
+        <v>0.1096538097128051</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0585431368615953</v>
+        <v>-0.08525760284046767</v>
       </c>
       <c r="X13" t="n">
-        <v>0.004262424384486914</v>
+        <v>-0.005373231892508559</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1073546768230707</v>
+        <v>-0.09466574392171224</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.08100685077857464</v>
+        <v>-0.1343002281628651</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2284147420512705</v>
+        <v>0.07228887843078613</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.04431562391292058</v>
+        <v>-0.0917295552104937</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2600109202350407</v>
+        <v>0.1461938968098248</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.179991226224739</v>
+        <v>0.06074834273955155</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2514214667564718</v>
+        <v>0.1283677193361362</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2240535223939912</v>
+        <v>0.07030234025585563</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.296970385344513</v>
+        <v>0.1179326128335236</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1371378743319386</v>
+        <v>0.1416761295759866</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1381745036134265</v>
+        <v>0.1436578256552618</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2043061452374026</v>
+        <v>0.08214399278724711</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.1117606133567508</v>
+        <v>0.0150752143106</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.1023033055007317</v>
+        <v>-0.1277328848145007</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.02645050618989897</v>
+        <v>0.05177513008139801</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.06202062266535006</v>
+        <v>0.07339246971253018</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.140491286254957</v>
+        <v>0.04214675004105423</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1771101501434756</v>
+        <v>0.04026768128961634</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003571473474954711</v>
+        <v>0.0188079203121424</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.2484830814162145</v>
+        <v>-0.149493094916571</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.1274287907460738</v>
+        <v>-0.009900642032787128</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.1146187498019572</v>
+        <v>0.005024585476235494</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.01435892239391238</v>
+        <v>0.03370223779251121</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.3864198062421532</v>
+        <v>0.2080987350435624</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1638482024562857</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.3453241012727103</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.05267689233523905</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.09814367495601811</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.07854110129772936</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.02035448914499858</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.07396132103269616</v>
       </c>
     </row>
     <row r="14">
@@ -2487,145 +2781,166 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.00931230949382297</v>
+        <v>-0.02031697272406424</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1111697454962486</v>
+        <v>0.08431162283892255</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.06041945162979315</v>
+        <v>-0.04541982085985333</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05911869267068982</v>
+        <v>-0.1014691029011309</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04022916989976748</v>
+        <v>0.07799163320206677</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.07132962764448499</v>
+        <v>-0.06134501559716155</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.07623624782346086</v>
+        <v>-0.1213789538748409</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06042891178150066</v>
+        <v>0.05877157472672545</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.03099105033020036</v>
+        <v>-0.05499390668032467</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08190437346475933</v>
+        <v>0.09303490081690853</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09465818094043063</v>
+        <v>0.0615423838646779</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.05011740004715102</v>
+        <v>0.1850511612061961</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.209294492419945</v>
+        <v>-0.2726656095988336</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1048095376063683</v>
+        <v>0.07469037995765433</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.09711744845667046</v>
+        <v>0.07084782910203201</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.09926031602264458</v>
+        <v>-0.1126730668382378</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0148069979468337</v>
+        <v>0.00631392196267344</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.009639891551805436</v>
+        <v>-0.04244989592868679</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1586780607817014</v>
+        <v>0.1503166758523957</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07094813365590424</v>
+        <v>0.1174536232299815</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.07644386196518244</v>
+        <v>-0.09851773832187806</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.03214783746896578</v>
+        <v>-0.0480833926530733</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.01572811362658094</v>
+        <v>0.007035934567311978</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.04075123644840745</v>
+        <v>-0.03644102762496004</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.04509077275648327</v>
+        <v>-0.07714713696882944</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.03522654794752336</v>
+        <v>-0.04513596768950091</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.04692070882601224</v>
+        <v>0.03927260968500303</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.001518183893143464</v>
+        <v>-0.01843120576380697</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01279633322097844</v>
+        <v>-0.02908958608453236</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.03826351286925156</v>
+        <v>-0.05316434178425288</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.01822659190731655</v>
+        <v>-0.01825697644614847</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.05279718073954819</v>
+        <v>0.067473570280472</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.04436107569631517</v>
+        <v>0.05636729274440407</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.06789832641361231</v>
+        <v>0.05913369533017518</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.003092562209894452</v>
+        <v>-0.07764386311935027</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.03654333944821013</v>
+        <v>0.03858721507363651</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.02999339799392101</v>
+        <v>-0.02253695522774743</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.08887125137339058</v>
+        <v>0.06387900067979847</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0417090546813336</v>
+        <v>0.06805524259980221</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01452401235980634</v>
+        <v>0.03734956486480687</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.004939781228437724</v>
+        <v>0.02797787354126907</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.05042212646585303</v>
+        <v>0.06997358084264711</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.06980722688947941</v>
+        <v>0.1043278811110261</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.09615487132319329</v>
+        <v>0.1186734428123374</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.03170563698488679</v>
+        <v>0.02933659984919215</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.01137812145021515</v>
+        <v>-0.030360690704092</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.01959990152489237</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.0322267987006969</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.05694416337724317</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.0175707717787368</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.09035145086286839</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0.06473964903144523</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.03161589616811954</v>
       </c>
     </row>
     <row r="15">
@@ -2635,145 +2950,166 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1608292768227431</v>
+        <v>0.113029208237141</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.002618359950095396</v>
+        <v>0.04751026295016244</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0141788984367829</v>
+        <v>-0.03210331166482896</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3081589269056427</v>
+        <v>0.2684455626205436</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1368405698935223</v>
+        <v>-0.03080502229483537</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1138621630816125</v>
+        <v>0.0923016287584893</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2847047122866223</v>
+        <v>0.2256673891891761</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07012820032438424</v>
+        <v>-0.02704443740013752</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2571577182687437</v>
+        <v>0.3742596556830837</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1688210467379411</v>
+        <v>0.3869466398266659</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.03501253999458167</v>
+        <v>-0.03048739573037867</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4952514692570114</v>
+        <v>-0.2654875403797134</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.209294492419945</v>
+        <v>-0.2726656095988336</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.415359605181589</v>
+        <v>0.5243720102110739</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3179874383527259</v>
+        <v>0.150662102832724</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004469092144542428</v>
+        <v>0.09138920848489068</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02816668813274127</v>
+        <v>0.00188615913746452</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2402572683499357</v>
+        <v>0.2232575079000033</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.422900477383213</v>
+        <v>-0.2583407621216594</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.09580428815248279</v>
+        <v>-0.05628023294135771</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2888860554869105</v>
+        <v>0.1813960627640997</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.04111753014455158</v>
+        <v>0.08076621214238267</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1666433169869624</v>
+        <v>0.1463947010584146</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.03008586831400008</v>
+        <v>-0.101474100695911</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.2102248187887747</v>
+        <v>0.1829199120722343</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2506470613762485</v>
+        <v>0.1972279984317493</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.05157488228954189</v>
+        <v>0.1085501149970379</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1587857235903386</v>
+        <v>0.1669666644359895</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1140088331406104</v>
+        <v>0.1083889341543681</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2141751897502172</v>
+        <v>0.1469187020971405</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1833026977425841</v>
+        <v>0.1138765751192702</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.01111404167763445</v>
+        <v>0.05384666557287832</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.01649478257513511</v>
+        <v>0.06567340109621851</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.00531642433306202</v>
+        <v>0.01444754198166607</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.1290054146154213</v>
+        <v>0.1828268182662884</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.002537854589751534</v>
+        <v>0.001013855070669609</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.02076400569654789</v>
+        <v>0.004389865741418964</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.01257927344425683</v>
+        <v>0.01281980472258036</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.03509224079365797</v>
+        <v>-0.02676141796414748</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.02792453541502259</v>
+        <v>-0.004802874619063173</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.0238366451345078</v>
+        <v>-0.03063970574296115</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.1506189918290665</v>
+        <v>-0.09098264195640905</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.1838130865281927</v>
+        <v>-0.1679141566949306</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.1723532702135688</v>
+        <v>-0.09693078480521278</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.04125819493876173</v>
+        <v>-0.01249460373696754</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2144791055469688</v>
+        <v>0.2082330803723523</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.3784424960782392</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.02639922454156223</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.1106053663432996</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.1060133015762211</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.06407251596811241</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.271737946961192</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.1989808435132211</v>
       </c>
     </row>
     <row r="16">
@@ -2783,145 +3119,166 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2382736686968275</v>
+        <v>0.07816263674239077</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2608331345451577</v>
+        <v>0.1255251210981429</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2004691684539251</v>
+        <v>-0.1174363192084952</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5378084986123908</v>
+        <v>0.3443687376885914</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1710975146249219</v>
+        <v>0.008809942006818006</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3600673680536377</v>
+        <v>0.1848371590970442</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4705795564429219</v>
+        <v>0.2452917105714467</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.005871812953530698</v>
+        <v>0.06116115465050893</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5642987744292742</v>
+        <v>0.7118076889037235</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3725299684761661</v>
+        <v>0.8319494832933113</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3832911220850172</v>
+        <v>0.3222325728898507</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5223960519923859</v>
+        <v>0.2901322106113485</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1048095376063683</v>
+        <v>0.07469037995765433</v>
       </c>
       <c r="O16" t="n">
-        <v>0.415359605181589</v>
+        <v>0.5243720102110739</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8195299750050321</v>
+        <v>0.2882269566916428</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.1745119501349606</v>
+        <v>-0.05831340292834208</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.03324538734745633</v>
+        <v>-0.02191325853709998</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4548682025479022</v>
+        <v>0.2066234464029314</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3073505537355035</v>
+        <v>0.2133516804114881</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0003145818198337323</v>
+        <v>0.03418589346536244</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3237224136066498</v>
+        <v>0.0910550432221474</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0488037386352123</v>
+        <v>0.08177211699100773</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.05044995551267822</v>
+        <v>0.02738747707648511</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.06890064264201656</v>
+        <v>-0.2549132738519501</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.432629619750102</v>
+        <v>0.2411809624320015</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2855725637257939</v>
+        <v>0.101220498790209</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.339519323898656</v>
+        <v>0.1793953814681</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.34761540992354</v>
+        <v>0.1873990574705917</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.3715142778158736</v>
+        <v>0.2299881144065435</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4345848342916893</v>
+        <v>0.2107326446262607</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.486665463773796</v>
+        <v>0.228156064367044</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1731833396793619</v>
+        <v>0.134606264220038</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.1765784885865097</v>
+        <v>0.1452916571452001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2320186091290181</v>
+        <v>0.1522764883419591</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.2472637462881076</v>
+        <v>0.1838000694863198</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.09547773670640775</v>
+        <v>-0.04222783973173171</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.03738372726300487</v>
+        <v>0.002765423809247164</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.08448898591431163</v>
+        <v>0.06979821615748848</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.1260531321008375</v>
+        <v>0.0356727260602503</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.161346742500851</v>
+        <v>0.0372834169056746</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.01847892243147197</v>
+        <v>-0.05743062382487321</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.3914977640303702</v>
+        <v>-0.2001302877768562</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.2919492854205141</v>
+        <v>-0.2072021205078812</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0.2574005089263018</v>
+        <v>-0.1164095296650015</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.014968648018751</v>
+        <v>-0.03084446659027948</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.6135805515591946</v>
+        <v>0.3728377004587167</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.5650034721395143</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.2361928574565279</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.2399564690233986</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.2097658161201254</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.0003645409019366314</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.3038552011161558</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.2870130828904522</v>
       </c>
     </row>
     <row r="17">
@@ -2931,145 +3288,166 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2451809314438915</v>
+        <v>0.2320571783242125</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2994745785077633</v>
+        <v>0.4674421914748393</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.189251413035684</v>
+        <v>-0.1783322490714215</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4762238290781774</v>
+        <v>0.4560663293079087</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1442027840490593</v>
+        <v>-0.1367913244540082</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3398504136832511</v>
+        <v>0.3272795044492487</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3978353748610639</v>
+        <v>0.3738127494687071</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.001391168173165931</v>
+        <v>0.006892828613742252</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2935980146037869</v>
+        <v>0.2825622712322184</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0532167173495391</v>
+        <v>0.06517504291838358</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3048563489705075</v>
+        <v>0.2875432065743173</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4458626560920056</v>
+        <v>0.1987339260441995</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09711744845667046</v>
+        <v>0.07084782910203201</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3179874383527259</v>
+        <v>0.150662102832724</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8195299750050321</v>
+        <v>0.2882269566916428</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.2026461810023214</v>
+        <v>-0.3496222667081557</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.01424067266643116</v>
+        <v>-0.0420143025801681</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5660239689357497</v>
+        <v>0.5459897453392947</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2446711042477113</v>
+        <v>0.2450000226564468</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001955653582048763</v>
+        <v>0.01214230468411573</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3806374949735077</v>
+        <v>0.3681639470773599</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1199159087939613</v>
+        <v>-0.1376077417687967</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1274007493923646</v>
+        <v>0.1502762490334664</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.06810058817691314</v>
+        <v>0.07348244818098838</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.387027287055185</v>
+        <v>0.3715245606460632</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.4095159788668317</v>
+        <v>0.4041495744768085</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4105310846598465</v>
+        <v>0.4037049982445671</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.4078874384904464</v>
+        <v>0.4077861230894299</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.3341385326854592</v>
+        <v>0.3310065364598836</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4393168079906711</v>
+        <v>0.4482103307986448</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.4897816541041921</v>
+        <v>0.4860692949824342</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1766299865563601</v>
+        <v>0.1975797469113458</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1715460633979903</v>
+        <v>0.1936912340845805</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.235458622783698</v>
+        <v>0.2003772522220403</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.211671225497985</v>
+        <v>0.2440624077183126</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.06529170091030921</v>
+        <v>-0.1139312895699194</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.05610437448487524</v>
+        <v>0.05860135825844475</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.08875807262015678</v>
+        <v>0.1024521238427998</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.1315249756402828</v>
+        <v>0.09895178903551514</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.1550892927711681</v>
+        <v>0.1035185071466202</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.0210957194631223</v>
+        <v>-0.04205710254594977</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.282142675089677</v>
+        <v>-0.2779088451167354</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0.2411493647411098</v>
+        <v>-0.2349282756511294</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.1776081439409462</v>
+        <v>-0.1585467650561223</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.01360377050464844</v>
+        <v>-0.01927331603724265</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.6058521846919148</v>
+        <v>0.6089550420477821</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.7473550740999032</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.377944486298073</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.205891734806674</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.4154892501002337</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.17707275587752</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.5546200513340656</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.2825563436673188</v>
       </c>
     </row>
     <row r="18">
@@ -3079,145 +3457,166 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.04254924407230871</v>
+        <v>-0.008962386564844183</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05098594829349382</v>
+        <v>-0.01277519729151235</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08937970396442449</v>
+        <v>-0.02594566140072222</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2954928791997097</v>
+        <v>0.1980644967825403</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02894211596581697</v>
+        <v>0.05593418424519243</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1738000004355764</v>
+        <v>-0.01459624485122176</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1795303237302894</v>
+        <v>0.09383680373166019</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02478221776872843</v>
+        <v>0.0176295976167304</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1409869252557819</v>
+        <v>0.06674016007647685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.05717705924973461</v>
+        <v>0.03807898552997514</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1065774427613611</v>
+        <v>-0.1653402840726587</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1370789860800536</v>
+        <v>-0.2054256023359318</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09926031602264458</v>
+        <v>-0.1126730668382378</v>
       </c>
       <c r="O18" t="n">
-        <v>0.004469092144542428</v>
+        <v>0.09138920848489068</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1745119501349606</v>
+        <v>-0.05831340292834208</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2026461810023214</v>
+        <v>-0.3496222667081557</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06335295010932306</v>
+        <v>0.04843696577445759</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6875010641666043</v>
+        <v>0.5585712049869651</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1694939517309994</v>
+        <v>-0.2129481385189043</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.02385478393704532</v>
+        <v>-0.02383067053244222</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4213779828759719</v>
+        <v>0.3207881481297928</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6097073002717445</v>
+        <v>0.5894304171455492</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5029006133459071</v>
+        <v>0.4382270022575634</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.05930575264821631</v>
+        <v>0.04549216160295466</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1688099758450787</v>
+        <v>0.08531934264134136</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.6164226354915432</v>
+        <v>0.5091157940392073</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1945608922413241</v>
+        <v>0.1324254979829408</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2071292147150615</v>
+        <v>0.1432946514669885</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1415956219198656</v>
+        <v>0.06225063924859641</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1839255830763797</v>
+        <v>0.07533743358123005</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1383469585718662</v>
+        <v>0.02465394909087679</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.05668190511597293</v>
+        <v>0.03326380553452446</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0468861089245278</v>
+        <v>0.02502020049399944</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.09216541758603876</v>
+        <v>0.03971335241726907</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.2080260631813586</v>
+        <v>0.1681247815554299</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.06198869077325236</v>
+        <v>0.07743386383368152</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.02435764842204789</v>
+        <v>-0.02391413692398917</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.04060644764100112</v>
+        <v>0.008656305718302471</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0814868780490997</v>
+        <v>0.04562702859713056</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.1017754273287806</v>
+        <v>0.05314160908392101</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.01619687460438848</v>
+        <v>0.0002082582553757781</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.01155159365279388</v>
+        <v>0.07638908585357303</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0.1418174353045152</v>
+        <v>-0.07483758801319154</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0.05187037608327888</v>
+        <v>0.01791400633551213</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.02869991393528543</v>
+        <v>-0.01506009986054029</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.3193338028320675</v>
+        <v>0.1807779140333277</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.2132395132056988</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.2691520526983202</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.1559475486800109</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.326473181584465</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.3607781816738335</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4576053777797011</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.1985005208538313</v>
       </c>
     </row>
     <row r="19">
@@ -3227,145 +3626,166 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.04998143020178656</v>
+        <v>0.03613648099968293</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004778969866349541</v>
+        <v>-0.01068106422476788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.007972512584302132</v>
+        <v>0.0223161067069179</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.03042928397960513</v>
+        <v>-0.02992412300406221</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02549431991421348</v>
+        <v>0.02857982179631793</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.06862797990733829</v>
+        <v>-0.107795805322077</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06306156732584109</v>
+        <v>-0.05978742679099373</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03232520534395899</v>
+        <v>-0.0325788616546463</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.05577487200473385</v>
+        <v>-0.06604675058278611</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0336417249168556</v>
+        <v>-0.04397974208244301</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.05797476914950474</v>
+        <v>-0.06748835683957323</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.06450259692146859</v>
+        <v>-0.06356301039149706</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0148069979468337</v>
+        <v>0.00631392196267344</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02816668813274127</v>
+        <v>0.00188615913746452</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.03324538734745633</v>
+        <v>-0.02191325853709998</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.01424067266643116</v>
+        <v>-0.0420143025801681</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06335295010932306</v>
+        <v>0.04843696577445759</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1346828130066006</v>
+        <v>0.09129668957211767</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.04714342189825919</v>
+        <v>-0.05729437345675602</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.005841504819311677</v>
+        <v>-0.009100272414566245</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0007095096206732528</v>
+        <v>0.0004582563359173683</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.02708004931716948</v>
+        <v>-0.02368048491802354</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1056065685409054</v>
+        <v>0.07410121398214284</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.007521744344233946</v>
+        <v>-0.00171803798743108</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.0475676296698801</v>
+        <v>-0.05084616428442841</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.1311847759895478</v>
+        <v>0.09592357677285131</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.02127214341393887</v>
+        <v>-0.03583032009665455</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.02373902704810468</v>
+        <v>-0.03500421112228926</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1126729626144407</v>
+        <v>-0.1118149103409677</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.09447952015593297</v>
+        <v>-0.09425307805511862</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.06760141323952229</v>
+        <v>-0.07138650671003338</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.1145418827291808</v>
+        <v>-0.1134989862958428</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.1278101712741404</v>
+        <v>-0.1220646413743753</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.02544364798879105</v>
+        <v>-0.03793420435369416</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.0182510390539991</v>
+        <v>-0.0003973090238664491</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.06108123777122684</v>
+        <v>0.04733215896540412</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.004295610410300116</v>
+        <v>0.0166991542909921</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.02679941302177242</v>
+        <v>-0.01413249899395547</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.06215737226918945</v>
+        <v>0.06866196309148545</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.1006451414659386</v>
+        <v>0.09886936241242321</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.00379287077999646</v>
+        <v>0.02515572947243297</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.1822275523477189</v>
+        <v>0.1805506735667712</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.0605708938467228</v>
+        <v>0.0554011166548371</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0.01190041091240638</v>
+        <v>-0.008764315562284273</v>
       </c>
       <c r="AU19" t="n">
-        <v>-0.02892087978229816</v>
+        <v>-0.03257881984008858</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.02560613000067955</v>
+        <v>-0.05451332587190124</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.03502082371852875</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.04652141406583364</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.01938511865322577</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.06769849623818894</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.06387123289007536</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.0444444381201575</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.005657630915561502</v>
       </c>
     </row>
     <row r="20">
@@ -3375,145 +3795,166 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2203472317221379</v>
+        <v>0.1947769519356069</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2631161671671479</v>
+        <v>0.3854565955200016</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2127413571582553</v>
+        <v>-0.2017758480876663</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5930074300286527</v>
+        <v>0.614207376935223</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07968586538833805</v>
+        <v>-0.1019595664820341</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3880520522217603</v>
+        <v>0.3023854049778036</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4359860588448988</v>
+        <v>0.4451251178232018</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01657261314789848</v>
+        <v>0.0009244218656472537</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3279556261553638</v>
+        <v>0.3427842114693724</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08353609322737154</v>
+        <v>0.09841980433192263</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1303773313455412</v>
+        <v>0.1130344944578868</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2081711301453267</v>
+        <v>-0.01444038399297258</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.009639891551805436</v>
+        <v>-0.04244989592868679</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2402572683499357</v>
+        <v>0.2232575079000033</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4548682025479022</v>
+        <v>0.2066234464029314</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5660239689357497</v>
+        <v>0.5459897453392947</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6875010641666043</v>
+        <v>0.5585712049869651</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1346828130066006</v>
+        <v>0.09129668957211767</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.03483604954490556</v>
+        <v>0.02066365225647846</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01891848317063466</v>
+        <v>-0.01672759755180516</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6300116462511143</v>
+        <v>0.6531669535326693</v>
       </c>
       <c r="X20" t="n">
-        <v>0.415771636105265</v>
+        <v>0.4304538851870777</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5212695109189945</v>
+        <v>0.5388480501081493</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1000631647377546</v>
+        <v>0.1133977068545599</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.4205627468142139</v>
+        <v>0.4273752234586608</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8254893743088426</v>
+        <v>0.8255205538102888</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.4616791337614463</v>
+        <v>0.4689239576055783</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.4699467715488598</v>
+        <v>0.4928527795910636</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3530214906658047</v>
+        <v>0.3871359625801085</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.4672474187951861</v>
+        <v>0.4961259503301711</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.4689974773229649</v>
+        <v>0.4761640797017903</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1664322281550388</v>
+        <v>0.2070058895737679</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.153326751270396</v>
+        <v>0.1946905105141721</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.2474328205188484</v>
+        <v>0.2187696683319085</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.3302239617120001</v>
+        <v>0.3949990853634431</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.009113210326003108</v>
+        <v>-0.04833558692802888</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.02064318971018644</v>
+        <v>0.03318209675674322</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.1015103956820856</v>
+        <v>0.09030815283679487</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.1702053360005616</v>
+        <v>0.1186083140891838</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.2079566951439599</v>
+        <v>0.1297441478219655</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.00241563955029363</v>
+        <v>-0.03562475830740771</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.2003024963065482</v>
+        <v>-0.2364919015669229</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0.2896161150008359</v>
+        <v>-0.3134152374744904</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0.1748545945989327</v>
+        <v>-0.1798107791738938</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.03652581962472267</v>
+        <v>-0.03097484195789028</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.7086244776126522</v>
+        <v>0.7302537651626411</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.8672773226018615</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.6069065060573356</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.3290769738803079</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.6708824217623492</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.1959697533576185</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.9275227059682924</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.4345877220985939</v>
       </c>
     </row>
     <row r="21">
@@ -3526,7 +3967,7 @@
         <v>0.01051433344513178</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1581545310600149</v>
+        <v>0.1382790698463231</v>
       </c>
       <c r="D21" t="n">
         <v>-0.06463838278416811</v>
@@ -3538,7 +3979,7 @@
         <v>-0.05494151543295182</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08301004780135807</v>
+        <v>0.1132002623642533</v>
       </c>
       <c r="H21" t="n">
         <v>0.1245498087937538</v>
@@ -3556,34 +3997,34 @@
         <v>0.3386720768341057</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6492117535742655</v>
+        <v>0.5911478882165804</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1586780607817014</v>
+        <v>0.1503166758523957</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.422900477383213</v>
+        <v>-0.2583407621216594</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3073505537355035</v>
+        <v>0.2133516804114881</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2446711042477113</v>
+        <v>0.2450000226564468</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.1694939517309994</v>
+        <v>-0.2129481385189043</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.04714342189825919</v>
+        <v>-0.05729437345675602</v>
       </c>
       <c r="T21" t="n">
-        <v>0.03483604954490556</v>
+        <v>0.02066365225647846</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1478709605476015</v>
+        <v>-0.1485124563826766</v>
       </c>
       <c r="W21" t="n">
         <v>-0.0645120486313151</v>
@@ -3595,7 +4036,7 @@
         <v>-0.1506728092079564</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.04150254643148286</v>
+        <v>-0.03824278690508153</v>
       </c>
       <c r="AA21" t="n">
         <v>0.1617212338067972</v>
@@ -3625,28 +4066,28 @@
         <v>0.0636312313832663</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1753151900797223</v>
+        <v>0.1611223697910389</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.06734146137698195</v>
+        <v>0.07616440279306204</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.0499106490837533</v>
+        <v>-0.07538872947254033</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.0001060915399839597</v>
+        <v>0.008412001443674794</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.02314772576357389</v>
+        <v>0.02717261542332889</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.06761555618047504</v>
+        <v>0.07558082226891437</v>
       </c>
       <c r="AP21" t="n">
         <v>0.07067398479896114</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.02304702486861692</v>
+        <v>-0.0009570502387469811</v>
       </c>
       <c r="AR21" t="n">
         <v>-0.1843618269865319</v>
@@ -3661,7 +4102,28 @@
         <v>0.06704913767140704</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2271222331314943</v>
+        <v>0.2362241608485904</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.1798485548765004</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.5830756620007724</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.1246347498562098</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.1172021708350955</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.1040656953886713</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.0599301740598937</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.05462502801646481</v>
       </c>
     </row>
     <row r="22">
@@ -3671,145 +4133,166 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.02785565775913115</v>
+        <v>-0.02739783085222267</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0480455708882969</v>
+        <v>0.04789604308002807</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05772902957154372</v>
+        <v>-0.05837331008026488</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0401501576699883</v>
+        <v>-0.04156678956230443</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1178209150813927</v>
+        <v>0.1211699892540699</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02740266233346421</v>
+        <v>0.04003930440607066</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0562613370010995</v>
+        <v>-0.05770147302676296</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09797365538453182</v>
+        <v>0.1002931551060214</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0133615596591872</v>
+        <v>-0.01639660104389544</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06481138093656827</v>
+        <v>0.0634818533393815</v>
       </c>
       <c r="L22" t="n">
-        <v>0.078179947986335</v>
+        <v>0.07532148067412894</v>
       </c>
       <c r="M22" t="n">
-        <v>0.06741847791011704</v>
+        <v>0.1096538097128051</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07094813365590424</v>
+        <v>0.1174536232299815</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.09580428815248279</v>
+        <v>-0.05628023294135771</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0003145818198337323</v>
+        <v>0.03418589346536244</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.001955653582048763</v>
+        <v>0.01214230468411573</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.02385478393704532</v>
+        <v>-0.02383067053244222</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.005841504819311677</v>
+        <v>-0.009100272414566245</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.01891848317063466</v>
+        <v>-0.01672759755180516</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1478709605476015</v>
+        <v>-0.1485124563826766</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.05453581198363544</v>
+        <v>-0.05301796214726752</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.01233990005227547</v>
+        <v>-0.01553559768825073</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.04651884838995064</v>
+        <v>0.0469489811687608</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.03794435022720095</v>
+        <v>-0.04657748271737827</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.03018016518537142</v>
+        <v>-0.03067429313129202</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.02383634126222052</v>
+        <v>-0.02274149193736182</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.02897558664625989</v>
+        <v>0.02991601206105038</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01850224063947348</v>
+        <v>0.01859733358045841</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.02611915378423335</v>
+        <v>-0.02599753262170197</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.02089105899687861</v>
+        <v>-0.02039563501098723</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.02453557957887926</v>
+        <v>-0.02328190689917788</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.02357684525591345</v>
+        <v>0.02839205903935828</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.02414108733457307</v>
+        <v>0.02898134135709278</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.04016122325953467</v>
+        <v>0.03598502870699877</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.02532375788905771</v>
+        <v>-0.04339155462423488</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.008555333868578055</v>
+        <v>-0.03511753969234761</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.03511363088677234</v>
+        <v>0.05723851555287245</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.03212140720908347</v>
+        <v>0.03647756140676565</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.02002462983851695</v>
+        <v>0.02470553517078088</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.04089439106034753</v>
+        <v>0.04177626125159246</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.007366524543625439</v>
+        <v>0.02717532197078318</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.03605962701722587</v>
+        <v>0.03834829088664252</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.009338706958155899</v>
+        <v>0.01038027438986323</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.07569419017568563</v>
+        <v>0.07968229712710719</v>
       </c>
       <c r="AU22" t="n">
-        <v>-0.04652388177402114</v>
+        <v>-0.04494840410455712</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.01684415429735896</v>
+        <v>-0.004889923139536271</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-0.004434693599053722</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.01141347698006117</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.01952999440031683</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-0.004099908668920523</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.04163084610752515</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.022764262734949</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.04567458712979108</v>
       </c>
     </row>
     <row r="23">
@@ -3822,7 +4305,7 @@
         <v>0.1205478702383639</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1260306265196436</v>
+        <v>0.1791926429023915</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1842126487010587</v>
@@ -3834,7 +4317,7 @@
         <v>-0.1941494887493022</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2729988557264337</v>
+        <v>0.2763830153638608</v>
       </c>
       <c r="H23" t="n">
         <v>0.4839494160445375</v>
@@ -3852,34 +4335,34 @@
         <v>0.09923253717822954</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0585431368615953</v>
+        <v>-0.08525760284046767</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.07644386196518244</v>
+        <v>-0.09851773832187806</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2888860554869105</v>
+        <v>0.1813960627640997</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3237224136066498</v>
+        <v>0.0910550432221474</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.3806374949735077</v>
+        <v>0.3681639470773599</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4213779828759719</v>
+        <v>0.3207881481297928</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0007095096206732528</v>
+        <v>0.0004582563359173683</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6300116462511143</v>
+        <v>0.6531669535326693</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0645120486313151</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.05453581198363544</v>
+        <v>-0.05301796214726752</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -3891,7 +4374,7 @@
         <v>0.3632519830232775</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1331152141960391</v>
+        <v>0.1300504180826919</v>
       </c>
       <c r="AA23" t="n">
         <v>0.4346480153946334</v>
@@ -3921,28 +4404,28 @@
         <v>0.1307824488060626</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1877032138358275</v>
+        <v>0.2312861092270518</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.259977425468249</v>
+        <v>0.3804190780098042</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.1150929634613426</v>
+        <v>-0.146385755815656</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.03535301658385278</v>
+        <v>0.03341602134452027</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.008106093328111857</v>
+        <v>-0.02577348989405163</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.04960382558403377</v>
+        <v>0.05406852100951617</v>
       </c>
       <c r="AP23" t="n">
         <v>0.05647920945400312</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.01428984497084799</v>
+        <v>-0.04409978017489277</v>
       </c>
       <c r="AR23" t="n">
         <v>-0.4684029202067294</v>
@@ -3957,7 +4440,28 @@
         <v>-0.01966884069152343</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.5606637627484448</v>
+        <v>0.5947706649972521</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.5782517875333385</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.6941971437508343</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.2438367338130943</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.42280990697165</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.197269666347525</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.6710224830870226</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.3220663141083442</v>
       </c>
     </row>
     <row r="24">
@@ -3970,7 +4474,7 @@
         <v>-0.01295210280608034</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01425946856643189</v>
+        <v>0.03872837510970988</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1165759362114533</v>
@@ -3982,7 +4486,7 @@
         <v>-0.06076932676159451</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1991075194121956</v>
+        <v>0.1499277168145839</v>
       </c>
       <c r="H24" t="n">
         <v>0.1938916711505843</v>
@@ -4000,34 +4504,34 @@
         <v>-0.03479076383059415</v>
       </c>
       <c r="M24" t="n">
-        <v>0.004262424384486914</v>
+        <v>-0.005373231892508559</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.03214783746896578</v>
+        <v>-0.0480833926530733</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.04111753014455158</v>
+        <v>0.08076621214238267</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.0488037386352123</v>
+        <v>0.08177211699100773</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1199159087939613</v>
+        <v>-0.1376077417687967</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6097073002717445</v>
+        <v>0.5894304171455492</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.02708004931716948</v>
+        <v>-0.02368048491802354</v>
       </c>
       <c r="T24" t="n">
-        <v>0.415771636105265</v>
+        <v>0.4304538851870777</v>
       </c>
       <c r="U24" t="n">
         <v>-0.0309049591425333</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.01233990005227547</v>
+        <v>-0.01553559768825073</v>
       </c>
       <c r="W24" t="n">
         <v>0.1363805887491449</v>
@@ -4039,7 +4543,7 @@
         <v>0.2266514841509449</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.06826254889694135</v>
+        <v>-0.06525859862636288</v>
       </c>
       <c r="AA24" t="n">
         <v>0.1806772375006158</v>
@@ -4069,28 +4573,28 @@
         <v>0.1208669797357013</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1080803026753633</v>
+        <v>0.1105132116520787</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.1997401475127928</v>
+        <v>0.255001786859636</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.09531652573608999</v>
+        <v>-0.1248696020293436</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.004972488417316049</v>
+        <v>-0.0009688868309234778</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.07242584517038067</v>
+        <v>0.06194707130037938</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.02238149805540992</v>
+        <v>0.02552278226732182</v>
       </c>
       <c r="AP24" t="n">
         <v>0.01152380023089732</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.001290144849284017</v>
+        <v>-0.02776882194440679</v>
       </c>
       <c r="AR24" t="n">
         <v>-0.2427277335071919</v>
@@ -4105,7 +4609,28 @@
         <v>-0.01026866886810395</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.2841076755947821</v>
+        <v>0.3139822242567327</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.2587706396305931</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.3935160149599109</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.1642293403801313</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.3061227724964301</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.2316487181493532</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.4048143188391862</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.1833850281156024</v>
       </c>
     </row>
     <row r="25">
@@ -4118,7 +4643,7 @@
         <v>0.1444936461070019</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1196899081513157</v>
+        <v>0.279172712322895</v>
       </c>
       <c r="D25" t="n">
         <v>-0.06002756363845823</v>
@@ -4130,7 +4655,7 @@
         <v>0.01298006009455062</v>
       </c>
       <c r="G25" t="n">
-        <v>0.102774516136891</v>
+        <v>0.09038345551871309</v>
       </c>
       <c r="H25" t="n">
         <v>-0.01872859098087966</v>
@@ -4148,34 +4673,34 @@
         <v>-0.1158058397977214</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1073546768230707</v>
+        <v>-0.09466574392171224</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.01572811362658094</v>
+        <v>0.007035934567311978</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1666433169869624</v>
+        <v>0.1463947010584146</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05044995551267822</v>
+        <v>0.02738747707648511</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1274007493923646</v>
+        <v>0.1502762490334664</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5029006133459071</v>
+        <v>0.4382270022575634</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1056065685409054</v>
+        <v>0.07410121398214284</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5212695109189945</v>
+        <v>0.5388480501081493</v>
       </c>
       <c r="U25" t="n">
         <v>-0.1506728092079564</v>
       </c>
       <c r="V25" t="n">
-        <v>0.04651884838995064</v>
+        <v>0.0469489811687608</v>
       </c>
       <c r="W25" t="n">
         <v>0.3632519830232775</v>
@@ -4187,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.1985967577071336</v>
+        <v>0.197607992281032</v>
       </c>
       <c r="AA25" t="n">
         <v>-0.01801150031444655</v>
@@ -4217,28 +4742,28 @@
         <v>-0.006144989896887168</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.04685377306989402</v>
+        <v>0.01741823332811838</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.09380957160591445</v>
+        <v>0.08378544865403784</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.0415704345195983</v>
+        <v>0.01017417603249014</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.02447779636611433</v>
+        <v>-0.0257480372767463</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.04429969112713476</v>
+        <v>0.02468354404361866</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.07070258356547476</v>
+        <v>0.0720279483309213</v>
       </c>
       <c r="AP25" t="n">
         <v>0.06397397487450993</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.007766971998717695</v>
+        <v>0.01433113872863791</v>
       </c>
       <c r="AR25" t="n">
         <v>0.06895972022171835</v>
@@ -4253,7 +4778,28 @@
         <v>-0.03601389283371469</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.1682131543007403</v>
+        <v>0.2090434330257377</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.3917367993150266</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.2348853913906301</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.04579504224298886</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.04835581883999099</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.01839194412095833</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0.4094471354377904</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0.09156171134119021</v>
       </c>
     </row>
     <row r="26">
@@ -4263,145 +4809,166 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.03442465807394676</v>
+        <v>0.03569160228646356</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.01778387050484175</v>
+        <v>0.002947235479246431</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09486962103415594</v>
+        <v>0.09592264877022069</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.183882234549221</v>
+        <v>-0.181779716663709</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0870008554363805</v>
+        <v>-0.08499358392920293</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.03845011208085553</v>
+        <v>-0.061518442784117</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1512358721209085</v>
+        <v>-0.148587792628355</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.05034971149413901</v>
+        <v>-0.04943385772244818</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2777312041386026</v>
+        <v>-0.2782327713828404</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2680236183359653</v>
+        <v>-0.2727126860482804</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.121960616778857</v>
+        <v>-0.1258949459016662</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.08100685077857464</v>
+        <v>-0.1343002281628651</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.04075123644840745</v>
+        <v>-0.03644102762496004</v>
       </c>
       <c r="O26" t="n">
-        <v>0.03008586831400008</v>
+        <v>-0.101474100695911</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.06890064264201656</v>
+        <v>-0.2549132738519501</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.06810058817691314</v>
+        <v>0.07348244818098838</v>
       </c>
       <c r="R26" t="n">
-        <v>0.05930575264821631</v>
+        <v>0.04549216160295466</v>
       </c>
       <c r="S26" t="n">
-        <v>0.007521744344233946</v>
+        <v>-0.00171803798743108</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1000631647377546</v>
+        <v>0.1133977068545599</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.04150254643148286</v>
+        <v>-0.03824278690508153</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.03794435022720095</v>
+        <v>-0.04657748271737827</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1331152141960391</v>
+        <v>0.1300504180826919</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.06826254889694135</v>
+        <v>-0.06525859862636288</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1985967577071336</v>
+        <v>0.197607992281032</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.1724228189734242</v>
+        <v>-0.169464493143015</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2560454085359487</v>
+        <v>0.2563541528695939</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.1239362352968973</v>
+        <v>-0.1202155164409204</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.154811427965023</v>
+        <v>-0.1508861569874182</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.1939619350539713</v>
+        <v>-0.1874101473766289</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.0506338924022174</v>
+        <v>-0.04359486204079394</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.06443304718314422</v>
+        <v>-0.05711993714834826</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.1639409346113221</v>
+        <v>-0.150956448794217</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.1815592256199678</v>
+        <v>-0.1672814076662687</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-0.0901302726790343</v>
+        <v>-0.09368911455724784</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.07009060989258577</v>
+        <v>-0.1155348015744279</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0373123850329696</v>
+        <v>0.03912830493311791</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.02460035869053165</v>
+        <v>-0.02668198295128936</v>
       </c>
       <c r="AN26" t="n">
-        <v>-0.0516133660614797</v>
+        <v>-0.05056386618150607</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.01452511601598093</v>
+        <v>-0.01440640433500991</v>
       </c>
       <c r="AP26" t="n">
-        <v>-0.01348991719842701</v>
+        <v>-0.01324453760876608</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.06234072400437926</v>
+        <v>0.03612416252755819</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.1759184083061004</v>
+        <v>0.1726709478684879</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.1516695471769221</v>
+        <v>0.1509694371493783</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.06280547563647422</v>
+        <v>0.06372467345518155</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.03168720650065465</v>
+        <v>0.03311976038816708</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.1359073708421409</v>
+        <v>-0.1442780016120567</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0.01612089137456612</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.0366271227316587</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-0.1478385009223542</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-0.1065270549092127</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.04325355561788625</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-0.01228966795605928</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-0.204296404039238</v>
       </c>
     </row>
     <row r="27">
@@ -4414,7 +4981,7 @@
         <v>0.1274777934821109</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06786351851282853</v>
+        <v>0.1184997355344485</v>
       </c>
       <c r="D27" t="n">
         <v>-0.1579333480504451</v>
@@ -4426,7 +4993,7 @@
         <v>-0.02670668967363533</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2826198480701212</v>
+        <v>0.2952402610447823</v>
       </c>
       <c r="H27" t="n">
         <v>0.7161221955033013</v>
@@ -4444,34 +5011,34 @@
         <v>0.2547068310561876</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2284147420512705</v>
+        <v>0.07228887843078613</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.04509077275648327</v>
+        <v>-0.07714713696882944</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2102248187887747</v>
+        <v>0.1829199120722343</v>
       </c>
       <c r="P27" t="n">
-        <v>0.432629619750102</v>
+        <v>0.2411809624320015</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.387027287055185</v>
+        <v>0.3715245606460632</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1688099758450787</v>
+        <v>0.08531934264134136</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0475676296698801</v>
+        <v>-0.05084616428442841</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4205627468142139</v>
+        <v>0.4273752234586608</v>
       </c>
       <c r="U27" t="n">
         <v>0.1617212338067972</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.03018016518537142</v>
+        <v>-0.03067429313129202</v>
       </c>
       <c r="W27" t="n">
         <v>0.4346480153946334</v>
@@ -4483,7 +5050,7 @@
         <v>-0.01801150031444655</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.1724228189734242</v>
+        <v>-0.169464493143015</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -4513,28 +5080,28 @@
         <v>0.2320768380286714</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.2210912471425065</v>
+        <v>0.2805192256550466</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.2592538838766663</v>
+        <v>0.393337981136203</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.1058589066069794</v>
+        <v>-0.1497232795686641</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.02233180850470162</v>
+        <v>0.03596386168414854</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.03078812658972638</v>
+        <v>0.01830541307271336</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.06235357457300738</v>
+        <v>0.06552242668530994</v>
       </c>
       <c r="AP27" t="n">
         <v>0.06719488150763069</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.05409484300151531</v>
+        <v>-0.10116052967878</v>
       </c>
       <c r="AR27" t="n">
         <v>-0.5292474125826893</v>
@@ -4549,7 +5116,28 @@
         <v>0.002046548651976242</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.6595997207286626</v>
+        <v>0.6678933348195355</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.4947600900446236</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.4649874832395979</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.3167641731470777</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0.3834106947106985</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0.116040568176363</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0.5734116343047393</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.532317957490831</v>
       </c>
     </row>
     <row r="28">
@@ -4562,7 +5150,7 @@
         <v>0.2213962408076297</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1900147776254092</v>
+        <v>0.3601314045179373</v>
       </c>
       <c r="D28" t="n">
         <v>-0.1371484480047782</v>
@@ -4574,7 +5162,7 @@
         <v>-0.05758316611286549</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2795678875257759</v>
+        <v>0.2332534120233238</v>
       </c>
       <c r="H28" t="n">
         <v>0.2979027751875958</v>
@@ -4592,34 +5180,34 @@
         <v>0.02671252119798431</v>
       </c>
       <c r="M28" t="n">
-        <v>0.04431562391292058</v>
+        <v>-0.0917295552104937</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.03522654794752336</v>
+        <v>-0.04513596768950091</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2506470613762485</v>
+        <v>0.1972279984317493</v>
       </c>
       <c r="P28" t="n">
-        <v>0.2855725637257939</v>
+        <v>0.101220498790209</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4095159788668317</v>
+        <v>0.4041495744768085</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6164226354915432</v>
+        <v>0.5091157940392073</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1311847759895478</v>
+        <v>0.09592357677285131</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8254893743088426</v>
+        <v>0.8255205538102888</v>
       </c>
       <c r="U28" t="n">
         <v>-0.05327523612339723</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.02383634126222052</v>
+        <v>-0.02274149193736182</v>
       </c>
       <c r="W28" t="n">
         <v>0.5547842535334832</v>
@@ -4631,7 +5219,7 @@
         <v>0.6766199357426493</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2560454085359487</v>
+        <v>0.2563541528695939</v>
       </c>
       <c r="AA28" t="n">
         <v>0.2872785432788034</v>
@@ -4661,28 +5249,28 @@
         <v>0.08054653810911938</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.1659838837149328</v>
+        <v>0.1558969219659544</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.2341915878315985</v>
+        <v>0.2607407798838453</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.004151299023856403</v>
+        <v>-0.02721764398119594</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.006683241010939592</v>
+        <v>-0.007059791459624333</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.05938259955941094</v>
+        <v>0.04000090642642068</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.08375734951492432</v>
+        <v>0.09234779406621493</v>
       </c>
       <c r="AP28" t="n">
         <v>0.08919262262260741</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.02476288416358408</v>
+        <v>-0.006327997173870501</v>
       </c>
       <c r="AR28" t="n">
         <v>-0.09695522283693357</v>
@@ -4697,7 +5285,28 @@
         <v>-0.03451635430217406</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.5337231555820273</v>
+        <v>0.53442240020944</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0.6749905840460861</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.4602733044409125</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.1979324967648889</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.1585613980456644</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0.1007337830363767</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0.7250705648714856</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.311235978216522</v>
       </c>
     </row>
     <row r="29">
@@ -4710,7 +5319,7 @@
         <v>0.04401764156165535</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2713640096245423</v>
+        <v>0.3277648971412582</v>
       </c>
       <c r="D29" t="n">
         <v>-0.2020193615126488</v>
@@ -4722,7 +5331,7 @@
         <v>-0.02381997776166213</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2470152773621434</v>
+        <v>0.2242629866920038</v>
       </c>
       <c r="H29" t="n">
         <v>0.2493346113871079</v>
@@ -4740,34 +5349,34 @@
         <v>0.1862907347285402</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2600109202350407</v>
+        <v>0.1461938968098248</v>
       </c>
       <c r="N29" t="n">
-        <v>0.04692070882601224</v>
+        <v>0.03927260968500303</v>
       </c>
       <c r="O29" t="n">
-        <v>0.05157488228954189</v>
+        <v>0.1085501149970379</v>
       </c>
       <c r="P29" t="n">
-        <v>0.339519323898656</v>
+        <v>0.1793953814681</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4105310846598465</v>
+        <v>0.4037049982445671</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1945608922413241</v>
+        <v>0.1324254979829408</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.02127214341393887</v>
+        <v>-0.03583032009665455</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4616791337614463</v>
+        <v>0.4689239576055783</v>
       </c>
       <c r="U29" t="n">
         <v>0.1379277084271985</v>
       </c>
       <c r="V29" t="n">
-        <v>0.02897558664625989</v>
+        <v>0.02991601206105038</v>
       </c>
       <c r="W29" t="n">
         <v>0.2436705030799112</v>
@@ -4779,7 +5388,7 @@
         <v>0.1075696809913239</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.1239362352968973</v>
+        <v>-0.1202155164409204</v>
       </c>
       <c r="AA29" t="n">
         <v>0.2564085073820082</v>
@@ -4809,28 +5418,28 @@
         <v>0.198003024576629</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.2000187957590239</v>
+        <v>0.1890982727864128</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.1694053271312014</v>
+        <v>0.20754296320591</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.02482186853706847</v>
+        <v>-0.05430600539004973</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.01125723899277491</v>
+        <v>0.02439140024290828</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.1845302695168488</v>
+        <v>0.1890114405166963</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.09507352203619873</v>
+        <v>0.1020808289020022</v>
       </c>
       <c r="AP29" t="n">
         <v>0.0956214443970938</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.001408605443045122</v>
+        <v>0.006561642332132116</v>
       </c>
       <c r="AR29" t="n">
         <v>-0.1485435634518603</v>
@@ -4845,7 +5454,28 @@
         <v>-0.02409556498069923</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.4669288367515272</v>
+        <v>0.4894495451574806</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.4729563532277896</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.3316520101674357</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.254477816945015</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0.3968093991083304</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>-0.02670994797470827</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0.4828694250074495</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.308361041462254</v>
       </c>
     </row>
     <row r="30">
@@ -4858,7 +5488,7 @@
         <v>0.08442317470266189</v>
       </c>
       <c r="C30" t="n">
-        <v>0.185332150761069</v>
+        <v>0.2755531461584911</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1931116694104817</v>
@@ -4870,7 +5500,7 @@
         <v>-0.05689876783960997</v>
       </c>
       <c r="G30" t="n">
-        <v>0.274949821510542</v>
+        <v>0.2525214140819323</v>
       </c>
       <c r="H30" t="n">
         <v>0.3617980012491556</v>
@@ -4888,34 +5518,34 @@
         <v>0.16690233895138</v>
       </c>
       <c r="M30" t="n">
-        <v>0.179991226224739</v>
+        <v>0.06074834273955155</v>
       </c>
       <c r="N30" t="n">
-        <v>0.001518183893143464</v>
+        <v>-0.01843120576380697</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1587857235903386</v>
+        <v>0.1669666644359895</v>
       </c>
       <c r="P30" t="n">
-        <v>0.34761540992354</v>
+        <v>0.1873990574705917</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4078874384904464</v>
+        <v>0.4077861230894299</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2071292147150615</v>
+        <v>0.1432946514669885</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.02373902704810468</v>
+        <v>-0.03500421112228926</v>
       </c>
       <c r="T30" t="n">
-        <v>0.4699467715488598</v>
+        <v>0.4928527795910636</v>
       </c>
       <c r="U30" t="n">
         <v>0.07765317165290073</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01850224063947348</v>
+        <v>0.01859733358045841</v>
       </c>
       <c r="W30" t="n">
         <v>0.2968569691900066</v>
@@ -4927,7 +5557,7 @@
         <v>0.09415756935170283</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.154811427965023</v>
+        <v>-0.1508861569874182</v>
       </c>
       <c r="AA30" t="n">
         <v>0.3538058543472556</v>
@@ -4957,28 +5587,28 @@
         <v>0.2105071646081392</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.2186638206949023</v>
+        <v>0.2250644915930202</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.1681111795870883</v>
+        <v>0.2388187763767621</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.04269666873538806</v>
+        <v>-0.07710896194085969</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.03579268942805653</v>
+        <v>0.05055531292931961</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.1500020411328118</v>
+        <v>0.1600184997667562</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.04873726338282511</v>
+        <v>0.05026578715546529</v>
       </c>
       <c r="AP30" t="n">
         <v>0.05438036797275444</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.02087158458785544</v>
+        <v>-0.04280995139045164</v>
       </c>
       <c r="AR30" t="n">
         <v>-0.2264463761521135</v>
@@ -4993,7 +5623,28 @@
         <v>-0.05129296357580812</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.520437605950402</v>
+        <v>0.5463621304447582</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.4980210470699335</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.3270755937235091</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.27365290254957</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.395016244651265</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.0136598907666629</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.5387442571560837</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.363407764367706</v>
       </c>
     </row>
     <row r="31">
@@ -5006,7 +5657,7 @@
         <v>0.09236304001051403</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1247560997887132</v>
+        <v>0.1908356310209044</v>
       </c>
       <c r="D31" t="n">
         <v>-0.2365268891815986</v>
@@ -5018,7 +5669,7 @@
         <v>-0.1712450021169971</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2759213444756037</v>
+        <v>0.3336023101645342</v>
       </c>
       <c r="H31" t="n">
         <v>0.5190541754450954</v>
@@ -5036,34 +5687,34 @@
         <v>0.2513665576239758</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2514214667564718</v>
+        <v>0.1283677193361362</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.01279633322097844</v>
+        <v>-0.02908958608453236</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1140088331406104</v>
+        <v>0.1083889341543681</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3715142778158736</v>
+        <v>0.2299881144065435</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3341385326854592</v>
+        <v>0.3310065364598836</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1415956219198656</v>
+        <v>0.06225063924859641</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.1126729626144407</v>
+        <v>-0.1118149103409677</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3530214906658047</v>
+        <v>0.3871359625801085</v>
       </c>
       <c r="U31" t="n">
         <v>0.1546216713837085</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.02611915378423335</v>
+        <v>-0.02599753262170197</v>
       </c>
       <c r="W31" t="n">
         <v>0.4075878124190781</v>
@@ -5075,7 +5726,7 @@
         <v>-0.01169519768998247</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.1939619350539713</v>
+        <v>-0.1874101473766289</v>
       </c>
       <c r="AA31" t="n">
         <v>0.4745697706150971</v>
@@ -5105,28 +5756,28 @@
         <v>0.4818128798740051</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.2515289411211353</v>
+        <v>0.292302643177017</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.2024732217403711</v>
+        <v>0.353969758580214</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.1876632041219479</v>
+        <v>-0.2237255253061191</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.03464209419813473</v>
+        <v>0.03917643775447112</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.04107423267022405</v>
+        <v>0.04199599860895281</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.02877423659757066</v>
+        <v>0.03261499031119501</v>
       </c>
       <c r="AP31" t="n">
         <v>0.03160347741993789</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.003351615158596792</v>
+        <v>-0.02089026705010226</v>
       </c>
       <c r="AR31" t="n">
         <v>-0.5947864748167557</v>
@@ -5141,7 +5792,28 @@
         <v>0.001466836264747029</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.5492467563332118</v>
+        <v>0.6048776883261389</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.4465661721197558</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.4612545904554048</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.2933021784866018</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.3450604812427399</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.02336351797809936</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.5043790671623233</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.3422318142793827</v>
       </c>
     </row>
     <row r="32">
@@ -5154,7 +5826,7 @@
         <v>0.1652286072073651</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1548707397535409</v>
+        <v>0.2720103419891267</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1949837929977347</v>
@@ -5166,7 +5838,7 @@
         <v>-0.1857575105783635</v>
       </c>
       <c r="G32" t="n">
-        <v>0.361944566177457</v>
+        <v>0.3871512411356073</v>
       </c>
       <c r="H32" t="n">
         <v>0.5263901811148737</v>
@@ -5184,34 +5856,34 @@
         <v>0.2528300922970061</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2240535223939912</v>
+        <v>0.07030234025585563</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.03826351286925156</v>
+        <v>-0.05316434178425288</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2141751897502172</v>
+        <v>0.1469187020971405</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4345848342916893</v>
+        <v>0.2107326446262607</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4393168079906711</v>
+        <v>0.4482103307986448</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1839255830763797</v>
+        <v>0.07533743358123005</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.09447952015593297</v>
+        <v>-0.09425307805511862</v>
       </c>
       <c r="T32" t="n">
-        <v>0.4672474187951861</v>
+        <v>0.4961259503301711</v>
       </c>
       <c r="U32" t="n">
         <v>0.1318812244061948</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.02089105899687861</v>
+        <v>-0.02039563501098723</v>
       </c>
       <c r="W32" t="n">
         <v>0.4696720432676275</v>
@@ -5223,7 +5895,7 @@
         <v>0.08610643768835281</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.0506338924022174</v>
+        <v>-0.04359486204079394</v>
       </c>
       <c r="AA32" t="n">
         <v>0.5098096082161486</v>
@@ -5253,28 +5925,28 @@
         <v>0.5684077627408407</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.2263421384698597</v>
+        <v>0.2524366322862938</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.2135694455896917</v>
+        <v>0.3359194309544649</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.1514341600268373</v>
+        <v>-0.1987190216879421</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.0357652851464537</v>
+        <v>0.03397494224998654</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.05049379192719832</v>
+        <v>0.03602278860372295</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.0209335310414654</v>
+        <v>0.02155386748641654</v>
       </c>
       <c r="AP32" t="n">
         <v>0.02438136637744539</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.04308012810223056</v>
+        <v>-0.05696476707828435</v>
       </c>
       <c r="AR32" t="n">
         <v>-0.5387273901503354</v>
@@ -5289,7 +5961,28 @@
         <v>-0.03911690411283703</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.6404091972583513</v>
+        <v>0.6806248726581898</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.5479549147472607</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.4835776192500575</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.2280865089015486</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.3877198888288143</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.01597534557079376</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0.5901455589024103</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.3684704204036856</v>
       </c>
     </row>
     <row r="33">
@@ -5302,7 +5995,7 @@
         <v>0.2014733531683406</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1804027551511163</v>
+        <v>0.3220483813817084</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1734720207634409</v>
@@ -5314,7 +6007,7 @@
         <v>-0.1515213705702294</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3708841528088984</v>
+        <v>0.3683963625021248</v>
       </c>
       <c r="H33" t="n">
         <v>0.495777619844057</v>
@@ -5332,34 +6025,34 @@
         <v>0.256818847725129</v>
       </c>
       <c r="M33" t="n">
-        <v>0.296970385344513</v>
+        <v>0.1179326128335236</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.01822659190731655</v>
+        <v>-0.01825697644614847</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1833026977425841</v>
+        <v>0.1138765751192702</v>
       </c>
       <c r="P33" t="n">
-        <v>0.486665463773796</v>
+        <v>0.228156064367044</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4897816541041921</v>
+        <v>0.4860692949824342</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1383469585718662</v>
+        <v>0.02465394909087679</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.06760141323952229</v>
+        <v>-0.07138650671003338</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4689974773229649</v>
+        <v>0.4761640797017903</v>
       </c>
       <c r="U33" t="n">
         <v>0.1791894804202309</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.02453557957887926</v>
+        <v>-0.02328190689917788</v>
       </c>
       <c r="W33" t="n">
         <v>0.405656208454009</v>
@@ -5371,7 +6064,7 @@
         <v>0.06525252989881627</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.06443304718314422</v>
+        <v>-0.05711993714834826</v>
       </c>
       <c r="AA33" t="n">
         <v>0.4896055840727534</v>
@@ -5401,28 +6094,28 @@
         <v>0.5472594003778009</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.2246663071787632</v>
+        <v>0.2260501724687462</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.2414346721380878</v>
+        <v>0.3309916794471254</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.1217767195610043</v>
+        <v>-0.17138031225486</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0350867002081597</v>
+        <v>0.03165606111737291</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.05141176244520847</v>
+        <v>0.04020704170080835</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.06104727170205997</v>
+        <v>0.07040042755083924</v>
       </c>
       <c r="AP33" t="n">
         <v>0.08039320289663276</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.02739991441262492</v>
+        <v>-0.03549206911436919</v>
       </c>
       <c r="AR33" t="n">
         <v>-0.4794077252396767</v>
@@ -5437,7 +6130,28 @@
         <v>-0.02737794041855878</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.6234314389183624</v>
+        <v>0.6508876811435927</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.5530764767574698</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.4515669914588005</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.2283605883235673</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.3897060692053662</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>-0.05284508992101768</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0.5561646011580648</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.3594044756844515</v>
       </c>
     </row>
     <row r="34">
@@ -5450,7 +6164,7 @@
         <v>0.0131466444609965</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07931311436416157</v>
+        <v>0.1459727480380153</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1092183717467147</v>
@@ -5462,7 +6176,7 @@
         <v>0.01905962302472417</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1349470486962461</v>
+        <v>0.1836721198874053</v>
       </c>
       <c r="H34" t="n">
         <v>0.2190227252171138</v>
@@ -5480,34 +6194,34 @@
         <v>0.07687779970826029</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1371378743319386</v>
+        <v>0.1416761295759866</v>
       </c>
       <c r="N34" t="n">
-        <v>0.05279718073954819</v>
+        <v>0.067473570280472</v>
       </c>
       <c r="O34" t="n">
-        <v>0.01111404167763445</v>
+        <v>0.05384666557287832</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1731833396793619</v>
+        <v>0.134606264220038</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1766299865563601</v>
+        <v>0.1975797469113458</v>
       </c>
       <c r="R34" t="n">
-        <v>0.05668190511597293</v>
+        <v>0.03326380553452446</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.1145418827291808</v>
+        <v>-0.1134989862958428</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1664322281550388</v>
+        <v>0.2070058895737679</v>
       </c>
       <c r="U34" t="n">
         <v>0.05813980868610001</v>
       </c>
       <c r="V34" t="n">
-        <v>0.02357684525591345</v>
+        <v>0.02839205903935828</v>
       </c>
       <c r="W34" t="n">
         <v>0.1403033192441326</v>
@@ -5519,7 +6233,7 @@
         <v>-0.004644979826494758</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.1639409346113221</v>
+        <v>-0.150956448794217</v>
       </c>
       <c r="AA34" t="n">
         <v>0.2381543267004847</v>
@@ -5549,28 +6263,28 @@
         <v>0.9591716048953658</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.1195630393090043</v>
+        <v>0.1210786224088329</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.0624334444048472</v>
+        <v>0.1331559095335361</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.09482534980894419</v>
+        <v>-0.1249620420952516</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.03539498951648273</v>
+        <v>0.03477242201502548</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.06912156080623497</v>
+        <v>0.07396586497025015</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.03545026836247619</v>
+        <v>0.03249450869772092</v>
       </c>
       <c r="AP34" t="n">
         <v>0.03068823160375573</v>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.004784452329274739</v>
+        <v>-0.007003499141449557</v>
       </c>
       <c r="AR34" t="n">
         <v>-0.2868891569901496</v>
@@ -5585,7 +6299,28 @@
         <v>-0.006451034517181108</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.2738390740062236</v>
+        <v>0.3632583210486576</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0.2434353427985571</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0.1772655519279273</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.1162303143950766</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.2091196021502789</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>-0.01847403604351073</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0.2846425861158252</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0.2513078432785797</v>
       </c>
     </row>
     <row r="35">
@@ -5598,7 +6333,7 @@
         <v>0.01304726087886099</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0760971750740833</v>
+        <v>0.137060669163895</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1028635742197958</v>
@@ -5610,7 +6345,7 @@
         <v>0.0167061861314389</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1337485063855376</v>
+        <v>0.1854581699229837</v>
       </c>
       <c r="H35" t="n">
         <v>0.2146800450003872</v>
@@ -5628,34 +6363,34 @@
         <v>0.07209979820896875</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1381745036134265</v>
+        <v>0.1436578256552618</v>
       </c>
       <c r="N35" t="n">
-        <v>0.04436107569631517</v>
+        <v>0.05636729274440407</v>
       </c>
       <c r="O35" t="n">
-        <v>0.01649478257513511</v>
+        <v>0.06567340109621851</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1765784885865097</v>
+        <v>0.1452916571452001</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1715460633979903</v>
+        <v>0.1936912340845805</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0468861089245278</v>
+        <v>0.02502020049399944</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.1278101712741404</v>
+        <v>-0.1220646413743753</v>
       </c>
       <c r="T35" t="n">
-        <v>0.153326751270396</v>
+        <v>0.1946905105141721</v>
       </c>
       <c r="U35" t="n">
         <v>0.0636312313832663</v>
       </c>
       <c r="V35" t="n">
-        <v>0.02414108733457307</v>
+        <v>0.02898134135709278</v>
       </c>
       <c r="W35" t="n">
         <v>0.1307824488060626</v>
@@ -5667,7 +6402,7 @@
         <v>-0.006144989896887168</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.1815592256199678</v>
+        <v>-0.1672814076662687</v>
       </c>
       <c r="AA35" t="n">
         <v>0.2320768380286714</v>
@@ -5697,28 +6432,28 @@
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.1336938372868814</v>
+        <v>0.135781740703231</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.05209438327602149</v>
+        <v>0.1230941484277097</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.09794576645914013</v>
+        <v>-0.1306336279400032</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.0263539684894513</v>
+        <v>0.02707031510751975</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.07194302187370882</v>
+        <v>0.07578553050642116</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.03573930857219858</v>
+        <v>0.03277168915182672</v>
       </c>
       <c r="AP35" t="n">
         <v>0.03094669296012649</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-0.001663451678764586</v>
+        <v>0.003459037449678545</v>
       </c>
       <c r="AR35" t="n">
         <v>-0.2910317233700659</v>
@@ -5733,7 +6468,28 @@
         <v>-0.008895340223509464</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.2631907844703988</v>
+        <v>0.3567663738720898</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.2392997150013057</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.1761424574103401</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.1180680517956684</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.1980057088920089</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>-0.01614366607499205</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0.2759978438498207</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0.245315487883977</v>
       </c>
     </row>
     <row r="36">
@@ -5743,145 +6499,166 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.01677975886666707</v>
+        <v>-0.01055853844824409</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1716976872571128</v>
+        <v>0.1229153708307461</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1617167981801607</v>
+        <v>-0.1552034491984531</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2389233922491861</v>
+        <v>0.2832556297578568</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.003333699289385612</v>
+        <v>-0.03908477859755016</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1599905296183509</v>
+        <v>0.1631064118362469</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2079320871804168</v>
+        <v>0.2640730826792085</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04687398599885621</v>
+        <v>0.02763431985015695</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2527025451603133</v>
+        <v>0.302954539549606</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1241742761856272</v>
+        <v>0.1318166125841248</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2481288586557223</v>
+        <v>0.3156642176333909</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2043061452374026</v>
+        <v>0.08214399278724711</v>
       </c>
       <c r="N36" t="n">
-        <v>0.06789832641361231</v>
+        <v>0.05913369533017518</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.00531642433306202</v>
+        <v>0.01444754198166607</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2320186091290181</v>
+        <v>0.1522764883419591</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.235458622783698</v>
+        <v>0.2003772522220403</v>
       </c>
       <c r="R36" t="n">
-        <v>0.09216541758603876</v>
+        <v>0.03971335241726907</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.02544364798879105</v>
+        <v>-0.03793420435369416</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2474328205188484</v>
+        <v>0.2187696683319085</v>
       </c>
       <c r="U36" t="n">
-        <v>0.1753151900797223</v>
+        <v>0.1611223697910389</v>
       </c>
       <c r="V36" t="n">
-        <v>0.04016122325953467</v>
+        <v>0.03598502870699877</v>
       </c>
       <c r="W36" t="n">
-        <v>0.1877032138358275</v>
+        <v>0.2312861092270518</v>
       </c>
       <c r="X36" t="n">
-        <v>0.1080803026753633</v>
+        <v>0.1105132116520787</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.04685377306989402</v>
+        <v>0.01741823332811838</v>
       </c>
       <c r="Z36" t="n">
-        <v>-0.0901302726790343</v>
+        <v>-0.09368911455724784</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.2210912471425065</v>
+        <v>0.2805192256550466</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.1659838837149328</v>
+        <v>0.1558969219659544</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.2000187957590239</v>
+        <v>0.1890982727864128</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.2186638206949023</v>
+        <v>0.2250644915930202</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2515289411211353</v>
+        <v>0.292302643177017</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2263421384698597</v>
+        <v>0.2524366322862938</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.2246663071787632</v>
+        <v>0.2260501724687462</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.1195630393090043</v>
+        <v>0.1210786224088329</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.1336938372868814</v>
+        <v>0.135781740703231</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.05866060856588732</v>
+        <v>0.135100661695411</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.1259888880376007</v>
+        <v>-0.1651961974782286</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.03277063359357432</v>
+        <v>-0.02390576244052063</v>
       </c>
       <c r="AN36" t="n">
-        <v>-0.07418135123983238</v>
+        <v>-0.09081832199774954</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.07337820695645406</v>
+        <v>0.04128518471651868</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.05808095931124223</v>
+        <v>0.03968603020124328</v>
       </c>
       <c r="AQ36" t="n">
-        <v>-0.009551228238372496</v>
+        <v>0.005967129272482792</v>
       </c>
       <c r="AR36" t="n">
-        <v>-0.2235511405738582</v>
+        <v>-0.3061634590136772</v>
       </c>
       <c r="AS36" t="n">
-        <v>-0.2043179079537525</v>
+        <v>-0.284595378370627</v>
       </c>
       <c r="AT36" t="n">
-        <v>-0.1827806511413796</v>
+        <v>-0.2641204010536209</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.02227045100925495</v>
+        <v>0.01891512641242749</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.3244134445681293</v>
+        <v>0.3430386514502506</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.2581466968643039</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.3094342677918531</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.5776882800974847</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.1819845225910144</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.01555845782064549</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0.2681256186925033</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.205634745590387</v>
       </c>
     </row>
     <row r="37">
@@ -5891,145 +6668,166 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.06960495214754152</v>
+        <v>0.07439822098927829</v>
       </c>
       <c r="C37" t="n">
-        <v>0.08477380884021633</v>
+        <v>0.1377543698927563</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.09313478427436463</v>
+        <v>-0.1420349890359973</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3088188233594516</v>
+        <v>0.4451009458903159</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03258881352158505</v>
+        <v>-0.1007830116005938</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1225283318319018</v>
+        <v>0.2070234255588875</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2915531145011275</v>
+        <v>0.4256107287322423</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0632802033987919</v>
+        <v>0.01778794828611252</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2539988660827411</v>
+        <v>0.3796758207222896</v>
       </c>
       <c r="K37" t="n">
-        <v>0.09670534790073362</v>
+        <v>0.144345252445279</v>
       </c>
       <c r="L37" t="n">
-        <v>0.08659009991280658</v>
+        <v>0.1203520939765843</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1117606133567508</v>
+        <v>0.0150752143106</v>
       </c>
       <c r="N37" t="n">
-        <v>0.003092562209894452</v>
+        <v>-0.07764386311935027</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1290054146154213</v>
+        <v>0.1828268182662884</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2472637462881076</v>
+        <v>0.1838000694863198</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.211671225497985</v>
+        <v>0.2440624077183126</v>
       </c>
       <c r="R37" t="n">
-        <v>0.2080260631813586</v>
+        <v>0.1681247815554299</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0182510390539991</v>
+        <v>-0.0003973090238664491</v>
       </c>
       <c r="T37" t="n">
-        <v>0.3302239617120001</v>
+        <v>0.3949990853634431</v>
       </c>
       <c r="U37" t="n">
-        <v>0.06734146137698195</v>
+        <v>0.07616440279306204</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.02532375788905771</v>
+        <v>-0.04339155462423488</v>
       </c>
       <c r="W37" t="n">
-        <v>0.259977425468249</v>
+        <v>0.3804190780098042</v>
       </c>
       <c r="X37" t="n">
-        <v>0.1997401475127928</v>
+        <v>0.255001786859636</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.09380957160591445</v>
+        <v>0.08378544865403784</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.07009060989258577</v>
+        <v>-0.1155348015744279</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.2592538838766663</v>
+        <v>0.393337981136203</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2341915878315985</v>
+        <v>0.2607407798838453</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1694053271312014</v>
+        <v>0.20754296320591</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.1681111795870883</v>
+        <v>0.2388187763767621</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.2024732217403711</v>
+        <v>0.353969758580214</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.2135694455896917</v>
+        <v>0.3359194309544649</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2414346721380878</v>
+        <v>0.3309916794471254</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.0624334444048472</v>
+        <v>0.1331559095335361</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.05209438327602149</v>
+        <v>0.1230941484277097</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.05866060856588732</v>
+        <v>0.135100661695411</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.09307931750864919</v>
+        <v>-0.1835662214587869</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.005842499340135754</v>
+        <v>0.02034625339833962</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.07430394385024314</v>
+        <v>0.004415690489740854</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.06076211148992589</v>
+        <v>0.03157182137261155</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.06009647834235919</v>
+        <v>0.03607990361214994</v>
       </c>
       <c r="AQ37" t="n">
-        <v>-0.01858373898764936</v>
+        <v>-0.03675090517163199</v>
       </c>
       <c r="AR37" t="n">
-        <v>-0.190920833248205</v>
+        <v>-0.3913107762211258</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.2298857678683388</v>
+        <v>-0.3869703695178712</v>
       </c>
       <c r="AT37" t="n">
-        <v>-0.2032691755054245</v>
+        <v>-0.349175874838192</v>
       </c>
       <c r="AU37" t="n">
-        <v>-0.05761936014209435</v>
+        <v>-0.06498642503756523</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.3158562271160548</v>
+        <v>0.459947910146742</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0.4059715509203315</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.3921734105431896</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.4930561929445007</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0.3368805768485049</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0.07357426170347608</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0.4547193337651752</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0.2972623010005083</v>
       </c>
     </row>
     <row r="38">
@@ -6039,145 +6837,166 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.02736610487444278</v>
+        <v>0.006146912610430093</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.01833973367221233</v>
+        <v>-0.01518603291759209</v>
       </c>
       <c r="D38" t="n">
-        <v>0.09509194788899258</v>
+        <v>0.1173664779032643</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1139368585956817</v>
+        <v>-0.1586481247560412</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07035618448230378</v>
+        <v>0.09247081485534324</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1099067972602167</v>
+        <v>-0.1856798514711146</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1495888058226588</v>
+        <v>-0.1806157564489581</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03509398209467423</v>
+        <v>0.03169632525125297</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1815325757817224</v>
+        <v>-0.205747965457807</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04119538732054864</v>
+        <v>-0.03898723887817345</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.09453206952634803</v>
+        <v>-0.1111821207154193</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.1023033055007317</v>
+        <v>-0.1277328848145007</v>
       </c>
       <c r="N38" t="n">
-        <v>0.03654333944821013</v>
+        <v>0.03858721507363651</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.002537854589751534</v>
+        <v>0.001013855070669609</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.09547773670640775</v>
+        <v>-0.04222783973173171</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.06529170091030921</v>
+        <v>-0.1139312895699194</v>
       </c>
       <c r="R38" t="n">
-        <v>0.06198869077325236</v>
+        <v>0.07743386383368152</v>
       </c>
       <c r="S38" t="n">
-        <v>0.06108123777122684</v>
+        <v>0.04733215896540412</v>
       </c>
       <c r="T38" t="n">
-        <v>0.009113210326003108</v>
+        <v>-0.04833558692802888</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.0499106490837533</v>
+        <v>-0.07538872947254033</v>
       </c>
       <c r="V38" t="n">
-        <v>-0.008555333868578055</v>
+        <v>-0.03511753969234761</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.1150929634613426</v>
+        <v>-0.146385755815656</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.09531652573608999</v>
+        <v>-0.1248696020293436</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.0415704345195983</v>
+        <v>0.01017417603249014</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.0373123850329696</v>
+        <v>0.03912830493311791</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0.1058589066069794</v>
+        <v>-0.1497232795686641</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.004151299023856403</v>
+        <v>-0.02721764398119594</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.02482186853706847</v>
+        <v>-0.05430600539004973</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.04269666873538806</v>
+        <v>-0.07710896194085969</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1876632041219479</v>
+        <v>-0.2237255253061191</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.1514341600268373</v>
+        <v>-0.1987190216879421</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.1217767195610043</v>
+        <v>-0.17138031225486</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.09482534980894419</v>
+        <v>-0.1249620420952516</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.09794576645914013</v>
+        <v>-0.1306336279400032</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.1259888880376007</v>
+        <v>-0.1651961974782286</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.09307931750864919</v>
+        <v>-0.1835662214587869</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.03730528278804604</v>
+        <v>-0.03894279542099215</v>
       </c>
       <c r="AN38" t="n">
-        <v>-0.0828642448326036</v>
+        <v>-0.08242260026959414</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.05420256229213977</v>
+        <v>0.00759536639479062</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.09841847940684452</v>
+        <v>0.0233327121737393</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.01836060013944773</v>
+        <v>0.03923594369352797</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.3862275537302375</v>
+        <v>0.4461203121704096</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.1933211449646071</v>
+        <v>0.2272246652718424</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.2580511418743375</v>
+        <v>0.2911820454334832</v>
       </c>
       <c r="AU38" t="n">
-        <v>-0.009915936955524949</v>
+        <v>0.00282136021500132</v>
       </c>
       <c r="AV38" t="n">
-        <v>-0.128577957925957</v>
+        <v>-0.2072631740152965</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>-0.1006880031145074</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>-0.1978583971139657</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.211331258138313</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>-0.05482950000630712</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-0.04348846938485919</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>-0.1004272139776529</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>-0.06879626429771911</v>
       </c>
     </row>
     <row r="39">
@@ -6187,145 +7006,166 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0234987244183133</v>
+        <v>0.0143966997370734</v>
       </c>
       <c r="C39" t="n">
-        <v>0.02042282958613336</v>
+        <v>0.0553752032449656</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.03380096584269817</v>
+        <v>-0.03249336311759071</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03037056713526447</v>
+        <v>0.02754596598754004</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02550366002413216</v>
+        <v>0.03883468262556374</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01914378432951321</v>
+        <v>0.04753954345656658</v>
       </c>
       <c r="H39" t="n">
-        <v>0.03693404140250921</v>
+        <v>0.04970139025731576</v>
       </c>
       <c r="I39" t="n">
-        <v>0.005196474953970466</v>
+        <v>0.01379328410463352</v>
       </c>
       <c r="J39" t="n">
-        <v>0.008096815232181972</v>
+        <v>0.00210532553658656</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.009149329224614857</v>
+        <v>-0.01387852719393275</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.01585361683462282</v>
+        <v>-0.003342920658525988</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02645050618989897</v>
+        <v>0.05177513008139801</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.02999339799392101</v>
+        <v>-0.02253695522774743</v>
       </c>
       <c r="O39" t="n">
-        <v>0.02076400569654789</v>
+        <v>0.004389865741418964</v>
       </c>
       <c r="P39" t="n">
-        <v>0.03738372726300487</v>
+        <v>0.002765423809247164</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.05610437448487524</v>
+        <v>0.05860135825844475</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.02435764842204789</v>
+        <v>-0.02391413692398917</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.004295610410300116</v>
+        <v>0.0166991542909921</v>
       </c>
       <c r="T39" t="n">
-        <v>0.02064318971018644</v>
+        <v>0.03318209675674322</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.0001060915399839597</v>
+        <v>0.008412001443674794</v>
       </c>
       <c r="V39" t="n">
-        <v>0.03511363088677234</v>
+        <v>0.05723851555287245</v>
       </c>
       <c r="W39" t="n">
-        <v>0.03535301658385278</v>
+        <v>0.03341602134452027</v>
       </c>
       <c r="X39" t="n">
-        <v>-0.004972488417316049</v>
+        <v>-0.0009688868309234778</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.02447779636611433</v>
+        <v>-0.0257480372767463</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.02460035869053165</v>
+        <v>-0.02668198295128936</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.02233180850470162</v>
+        <v>0.03596386168414854</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.006683241010939592</v>
+        <v>-0.007059791459624333</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.01125723899277491</v>
+        <v>0.02439140024290828</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.03579268942805653</v>
+        <v>0.05055531292931961</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.03464209419813473</v>
+        <v>0.03917643775447112</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0357652851464537</v>
+        <v>0.03397494224998654</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0350867002081597</v>
+        <v>0.03165606111737291</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.03539498951648273</v>
+        <v>0.03477242201502548</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.0263539684894513</v>
+        <v>0.02707031510751975</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-0.03277063359357432</v>
+        <v>-0.02390576244052063</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.005842499340135754</v>
+        <v>0.02034625339833962</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.03730528278804604</v>
+        <v>-0.03894279542099215</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>-0.0314358470390956</v>
+        <v>-0.03762714365598276</v>
       </c>
       <c r="AO39" t="n">
-        <v>-0.007991548872868936</v>
+        <v>-0.008918433504263114</v>
       </c>
       <c r="AP39" t="n">
-        <v>-0.007421994596364961</v>
+        <v>-0.008199167898643542</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.0003539652779393942</v>
+        <v>0.007221316339436908</v>
       </c>
       <c r="AR39" t="n">
-        <v>-0.03048695759754632</v>
+        <v>-0.02849790001807136</v>
       </c>
       <c r="AS39" t="n">
-        <v>-0.04410208223313953</v>
+        <v>-0.05178046647831222</v>
       </c>
       <c r="AT39" t="n">
-        <v>-0.01403999438094942</v>
+        <v>-0.01181192456574095</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.01864492540474369</v>
+        <v>0.009883399523441963</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.04458366533574836</v>
+        <v>0.05882693156315381</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.03905447760956973</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0.03718859027050601</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.09036841788404558</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.06108596000797413</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>-0.03858944206792053</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0.03728542675149699</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0.04801291838030565</v>
       </c>
     </row>
     <row r="40">
@@ -6335,145 +7175,166 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.02296873201099656</v>
+        <v>0.01832593015222203</v>
       </c>
       <c r="C40" t="n">
-        <v>0.04316037769525196</v>
+        <v>0.08751837576497702</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.06518217240407964</v>
+        <v>-0.05794917056905853</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0648863604935155</v>
+        <v>0.04998336722916914</v>
       </c>
       <c r="F40" t="n">
-        <v>0.05481052878611519</v>
+        <v>0.06154770796263515</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06224771119321619</v>
+        <v>0.03865821401417698</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0126882329502044</v>
+        <v>-0.003326157434690447</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02859288412589658</v>
+        <v>0.01816380923242146</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03439580927897198</v>
+        <v>0.02699806801220587</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03931131993286549</v>
+        <v>0.03676265871385045</v>
       </c>
       <c r="L40" t="n">
-        <v>0.04220682248103895</v>
+        <v>0.03790628162798328</v>
       </c>
       <c r="M40" t="n">
-        <v>0.06202062266535006</v>
+        <v>0.07339246971253018</v>
       </c>
       <c r="N40" t="n">
-        <v>0.08887125137339058</v>
+        <v>0.06387900067979847</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.01257927344425683</v>
+        <v>0.01281980472258036</v>
       </c>
       <c r="P40" t="n">
-        <v>0.08448898591431163</v>
+        <v>0.06979821615748848</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.08875807262015678</v>
+        <v>0.1024521238427998</v>
       </c>
       <c r="R40" t="n">
-        <v>0.04060644764100112</v>
+        <v>0.008656305718302471</v>
       </c>
       <c r="S40" t="n">
-        <v>0.02679941302177242</v>
+        <v>-0.01413249899395547</v>
       </c>
       <c r="T40" t="n">
-        <v>0.1015103956820856</v>
+        <v>0.09030815283679487</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02314772576357389</v>
+        <v>0.02717261542332889</v>
       </c>
       <c r="V40" t="n">
-        <v>0.03212140720908347</v>
+        <v>0.03647756140676565</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.008106093328111857</v>
+        <v>-0.02577348989405163</v>
       </c>
       <c r="X40" t="n">
-        <v>0.07242584517038067</v>
+        <v>0.06194707130037938</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.04429969112713476</v>
+        <v>0.02468354404361866</v>
       </c>
       <c r="Z40" t="n">
-        <v>-0.0516133660614797</v>
+        <v>-0.05056386618150607</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.03078812658972638</v>
+        <v>0.01830541307271336</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.05938259955941094</v>
+        <v>0.04000090642642068</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1845302695168488</v>
+        <v>0.1890114405166963</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.1500020411328118</v>
+        <v>0.1600184997667562</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.04107423267022405</v>
+        <v>0.04199599860895281</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.05049379192719832</v>
+        <v>0.03602278860372295</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.05141176244520847</v>
+        <v>0.04020704170080835</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.06912156080623497</v>
+        <v>0.07396586497025015</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.07194302187370882</v>
+        <v>0.07578553050642116</v>
       </c>
       <c r="AJ40" t="n">
-        <v>-0.07418135123983238</v>
+        <v>-0.09081832199774954</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.07430394385024314</v>
+        <v>0.004415690489740854</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.0828642448326036</v>
+        <v>-0.08242260026959414</v>
       </c>
       <c r="AM40" t="n">
-        <v>-0.0314358470390956</v>
+        <v>-0.03762714365598276</v>
       </c>
       <c r="AN40" t="n">
         <v>1</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.05130739451790557</v>
+        <v>0.0220843560402015</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.009267467794327073</v>
+        <v>-0.004102135286710629</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.03194576077490815</v>
+        <v>0.02419531184306942</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.05075528053243199</v>
+        <v>0.0605030001154836</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.03942954851506356</v>
+        <v>0.04140212172836528</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.09059557420830899</v>
+        <v>0.1083141243316737</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.01069410600378352</v>
+        <v>0.0220374207240637</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.1114465711429114</v>
+        <v>0.1058574774407744</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.1079028463568359</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.0250477860796118</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0.197030409648329</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.1073077198508168</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>-0.04441250878897959</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0.08475446203954393</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0.08126061986638175</v>
       </c>
     </row>
     <row r="41">
@@ -6483,145 +7344,166 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1141063586023839</v>
+        <v>0.1333509268377824</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0776723918801745</v>
+        <v>0.09725733278091506</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.04710024174230158</v>
+        <v>-0.05251125911772074</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06516584360589192</v>
+        <v>0.07265056252291785</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.001984942268184163</v>
+        <v>-0.008085053397001643</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0119283940295965</v>
+        <v>0.005661698818330052</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03476617239374453</v>
+        <v>0.03789537215966963</v>
       </c>
       <c r="I41" t="n">
-        <v>0.04438718368305009</v>
+        <v>0.04064725860066499</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02641484902600591</v>
+        <v>0.0287435892857033</v>
       </c>
       <c r="K41" t="n">
-        <v>0.008097674679767001</v>
+        <v>0.008180291844328594</v>
       </c>
       <c r="L41" t="n">
-        <v>0.04219029921216872</v>
+        <v>0.04259362651145121</v>
       </c>
       <c r="M41" t="n">
-        <v>0.140491286254957</v>
+        <v>0.04214675004105423</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0417090546813336</v>
+        <v>0.06805524259980221</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.03509224079365797</v>
+        <v>-0.02676141796414748</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1260531321008375</v>
+        <v>0.0356727260602503</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1315249756402828</v>
+        <v>0.09895178903551514</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0814868780490997</v>
+        <v>0.04562702859713056</v>
       </c>
       <c r="S41" t="n">
-        <v>0.06215737226918945</v>
+        <v>0.06866196309148545</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1702053360005616</v>
+        <v>0.1186083140891838</v>
       </c>
       <c r="U41" t="n">
-        <v>0.06761555618047504</v>
+        <v>0.07558082226891437</v>
       </c>
       <c r="V41" t="n">
-        <v>0.02002462983851695</v>
+        <v>0.02470553517078088</v>
       </c>
       <c r="W41" t="n">
-        <v>0.04960382558403377</v>
+        <v>0.05406852100951617</v>
       </c>
       <c r="X41" t="n">
-        <v>0.02238149805540992</v>
+        <v>0.02552278226732182</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.07070258356547476</v>
+        <v>0.0720279483309213</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.01452511601598093</v>
+        <v>-0.01440640433500991</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.06235357457300738</v>
+        <v>0.06552242668530994</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.08375734951492432</v>
+        <v>0.09234779406621493</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.09507352203619873</v>
+        <v>0.1020808289020022</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.04873726338282511</v>
+        <v>0.05026578715546529</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.02877423659757066</v>
+        <v>0.03261499031119501</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0209335310414654</v>
+        <v>0.02155386748641654</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.06104727170205997</v>
+        <v>0.07040042755083924</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.03545026836247619</v>
+        <v>0.03249450869772092</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.03573930857219858</v>
+        <v>0.03277168915182672</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.07337820695645406</v>
+        <v>0.04128518471651868</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.06076211148992589</v>
+        <v>0.03157182137261155</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.05420256229213977</v>
+        <v>0.00759536639479062</v>
       </c>
       <c r="AM41" t="n">
-        <v>-0.007991548872868936</v>
+        <v>-0.008918433504263114</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.05130739451790557</v>
+        <v>0.0220843560402015</v>
       </c>
       <c r="AO41" t="n">
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.8999237636059758</v>
+        <v>0.9173566892291762</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.02966865085402175</v>
+        <v>0.04736223619086898</v>
       </c>
       <c r="AR41" t="n">
-        <v>-0.007562564438009005</v>
+        <v>-0.008341432944055524</v>
       </c>
       <c r="AS41" t="n">
-        <v>-0.009673963912879861</v>
+        <v>-0.01276043727367931</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.01525382925357148</v>
+        <v>0.01455868660198485</v>
       </c>
       <c r="AU41" t="n">
-        <v>-0.05968893167526011</v>
+        <v>-0.05797934533969256</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.09240354949187314</v>
+        <v>0.06994885182203241</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.1169499100107334</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.09969766820306182</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.05868728796257727</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.1097644563020201</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>-0.02266400649411131</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0.1058103684447757</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.05401651248635892</v>
       </c>
     </row>
     <row r="42">
@@ -6634,7 +7516,7 @@
         <v>0.1517547790015385</v>
       </c>
       <c r="C42" t="n">
-        <v>0.09138095017275082</v>
+        <v>0.100574319100636</v>
       </c>
       <c r="D42" t="n">
         <v>-0.05332093096219565</v>
@@ -6646,7 +7528,7 @@
         <v>-0.0148851152876456</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01322812811560468</v>
+        <v>-0.01331000024092372</v>
       </c>
       <c r="H42" t="n">
         <v>0.05543523010076364</v>
@@ -6664,34 +7546,34 @@
         <v>0.0535813969539207</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1771101501434756</v>
+        <v>0.04026768128961634</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01452401235980634</v>
+        <v>0.03734956486480687</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.02792453541502259</v>
+        <v>-0.004802874619063173</v>
       </c>
       <c r="P42" t="n">
-        <v>0.161346742500851</v>
+        <v>0.0372834169056746</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.1550892927711681</v>
+        <v>0.1035185071466202</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1017754273287806</v>
+        <v>0.05314160908392101</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1006451414659386</v>
+        <v>0.09886936241242321</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2079566951439599</v>
+        <v>0.1297441478219655</v>
       </c>
       <c r="U42" t="n">
         <v>0.07067398479896114</v>
       </c>
       <c r="V42" t="n">
-        <v>0.04089439106034753</v>
+        <v>0.04177626125159246</v>
       </c>
       <c r="W42" t="n">
         <v>0.05647920945400312</v>
@@ -6703,7 +7585,7 @@
         <v>0.06397397487450993</v>
       </c>
       <c r="Z42" t="n">
-        <v>-0.01348991719842701</v>
+        <v>-0.01324453760876608</v>
       </c>
       <c r="AA42" t="n">
         <v>0.06719488150763069</v>
@@ -6733,28 +7615,28 @@
         <v>0.03094669296012649</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.05808095931124223</v>
+        <v>0.03968603020124328</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.06009647834235919</v>
+        <v>0.03607990361214994</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.09841847940684452</v>
+        <v>0.0233327121737393</v>
       </c>
       <c r="AM42" t="n">
-        <v>-0.007421994596364961</v>
+        <v>-0.008199167898643542</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.009267467794327073</v>
+        <v>-0.004102135286710629</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.8999237636059758</v>
+        <v>0.9173566892291762</v>
       </c>
       <c r="AP42" t="n">
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.007946212655798739</v>
+        <v>0.008672886090993813</v>
       </c>
       <c r="AR42" t="n">
         <v>-0.002821518527185536</v>
@@ -6769,7 +7651,28 @@
         <v>-0.04678599694605141</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.1154843047305477</v>
+        <v>0.07822320076903221</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.127725309968595</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.09621633025239522</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.05405345453898742</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.1284638226504768</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>-0.01742478397602201</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0.116973662716595</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.05986019862586168</v>
       </c>
     </row>
     <row r="43">
@@ -6779,145 +7682,166 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.05960573010301279</v>
+        <v>-0.04188524611986889</v>
       </c>
       <c r="C43" t="n">
-        <v>0.03806769201918332</v>
+        <v>0.08029769918252747</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.02863767848728298</v>
+        <v>-0.01868136474241074</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.03140621050074643</v>
+        <v>-0.08513084299391066</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06877680605724999</v>
+        <v>0.0792514540096167</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.02951224865746651</v>
+        <v>-0.05351138965223912</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.03930981826985685</v>
+        <v>-0.07667236394458131</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05164863916650527</v>
+        <v>-0.005534917029517625</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.04440369387701099</v>
+        <v>-0.08799698280011924</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.02324015718639813</v>
+        <v>-0.03534737041100905</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.01728125661742881</v>
+        <v>-0.04052241369718979</v>
       </c>
       <c r="M43" t="n">
-        <v>0.003571473474954711</v>
+        <v>0.0188079203121424</v>
       </c>
       <c r="N43" t="n">
-        <v>0.004939781228437724</v>
+        <v>0.02797787354126907</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.0238366451345078</v>
+        <v>-0.03063970574296115</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.01847892243147197</v>
+        <v>-0.05743062382487321</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.0210957194631223</v>
+        <v>-0.04205710254594977</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01619687460438848</v>
+        <v>0.0002082582553757781</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.00379287077999646</v>
+        <v>0.02515572947243297</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.00241563955029363</v>
+        <v>-0.03562475830740771</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.02304702486861692</v>
+        <v>-0.0009570502387469811</v>
       </c>
       <c r="V43" t="n">
-        <v>-0.007366524543625439</v>
+        <v>0.02717532197078318</v>
       </c>
       <c r="W43" t="n">
-        <v>-0.01428984497084799</v>
+        <v>-0.04409978017489277</v>
       </c>
       <c r="X43" t="n">
-        <v>0.001290144849284017</v>
+        <v>-0.02776882194440679</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.007766971998717695</v>
+        <v>0.01433113872863791</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.06234072400437926</v>
+        <v>0.03612416252755819</v>
       </c>
       <c r="AA43" t="n">
-        <v>-0.05409484300151531</v>
+        <v>-0.10116052967878</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.02476288416358408</v>
+        <v>-0.006327997173870501</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.001408605443045122</v>
+        <v>0.006561642332132116</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.02087158458785544</v>
+        <v>-0.04280995139045164</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.003351615158596792</v>
+        <v>-0.02089026705010226</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.04308012810223056</v>
+        <v>-0.05696476707828435</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.02739991441262492</v>
+        <v>-0.03549206911436919</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.004784452329274739</v>
+        <v>-0.007003499141449557</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.001663451678764586</v>
+        <v>0.003459037449678545</v>
       </c>
       <c r="AJ43" t="n">
-        <v>-0.009551228238372496</v>
+        <v>0.005967129272482792</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.01858373898764936</v>
+        <v>-0.03675090517163199</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.01836060013944773</v>
+        <v>0.03923594369352797</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0003539652779393942</v>
+        <v>0.007221316339436908</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.03194576077490815</v>
+        <v>0.02419531184306942</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.02966865085402175</v>
+        <v>0.04736223619086898</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.007946212655798739</v>
+        <v>0.008672886090993813</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.03454483824658241</v>
+        <v>0.08018035951407643</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.01060179377045422</v>
+        <v>0.0782271122096426</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.0290376191824257</v>
+        <v>0.04898201427126344</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.004906262452666604</v>
+        <v>0.05655274589888924</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.02118957964030325</v>
+        <v>-0.06705358033225921</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>-0.06133893782327564</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>-0.0364667252430471</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>-0.006177539529897094</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>-0.05784777492690173</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>-0.085397539802953</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>-0.0596143903510089</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>-0.01744565768846964</v>
       </c>
     </row>
     <row r="44">
@@ -6930,7 +7854,7 @@
         <v>-0.03732683663916023</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.01483155851922715</v>
+        <v>-0.02310161380799476</v>
       </c>
       <c r="D44" t="n">
         <v>0.2306483290843977</v>
@@ -6942,7 +7866,7 @@
         <v>0.3773254975104511</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3114785424298824</v>
+        <v>-0.4070914822471848</v>
       </c>
       <c r="H44" t="n">
         <v>-0.5975223201623887</v>
@@ -6960,34 +7884,34 @@
         <v>-0.2919829814293874</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.2484830814162145</v>
+        <v>-0.149493094916571</v>
       </c>
       <c r="N44" t="n">
-        <v>0.05042212646585303</v>
+        <v>0.06997358084264711</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.1506189918290665</v>
+        <v>-0.09098264195640905</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.3914977640303702</v>
+        <v>-0.2001302877768562</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.282142675089677</v>
+        <v>-0.2779088451167354</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.01155159365279388</v>
+        <v>0.07638908585357303</v>
       </c>
       <c r="S44" t="n">
-        <v>0.1822275523477189</v>
+        <v>0.1805506735667712</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.2003024963065482</v>
+        <v>-0.2364919015669229</v>
       </c>
       <c r="U44" t="n">
         <v>-0.1843618269865319</v>
       </c>
       <c r="V44" t="n">
-        <v>0.03605962701722587</v>
+        <v>0.03834829088664252</v>
       </c>
       <c r="W44" t="n">
         <v>-0.4684029202067294</v>
@@ -6999,7 +7923,7 @@
         <v>0.06895972022171835</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.1759184083061004</v>
+        <v>0.1726709478684879</v>
       </c>
       <c r="AA44" t="n">
         <v>-0.5292474125826893</v>
@@ -7029,28 +7953,28 @@
         <v>-0.2910317233700659</v>
       </c>
       <c r="AJ44" t="n">
-        <v>-0.2235511405738582</v>
+        <v>-0.3061634590136772</v>
       </c>
       <c r="AK44" t="n">
-        <v>-0.190920833248205</v>
+        <v>-0.3913107762211258</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.3862275537302375</v>
+        <v>0.4461203121704096</v>
       </c>
       <c r="AM44" t="n">
-        <v>-0.03048695759754632</v>
+        <v>-0.02849790001807136</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.05075528053243199</v>
+        <v>0.0605030001154836</v>
       </c>
       <c r="AO44" t="n">
-        <v>-0.007562564438009005</v>
+        <v>-0.008341432944055524</v>
       </c>
       <c r="AP44" t="n">
         <v>-0.002821518527185536</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.03454483824658241</v>
+        <v>0.08018035951407643</v>
       </c>
       <c r="AR44" t="n">
         <v>1</v>
@@ -7065,7 +7989,28 @@
         <v>0.05750015991008411</v>
       </c>
       <c r="AV44" t="n">
-        <v>-0.5233504175468142</v>
+        <v>-0.5872899969035876</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>-0.3570046176139451</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>-0.5225949607345096</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>-0.1532666451446972</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>-0.2729118244903806</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>-0.1216764383139707</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>-0.4132590036868121</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>-0.2196935518945018</v>
       </c>
     </row>
     <row r="45">
@@ -7078,7 +8023,7 @@
         <v>-0.07941546905825926</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.01461138554969105</v>
+        <v>-0.02933197518168441</v>
       </c>
       <c r="D45" t="n">
         <v>0.1779073131222352</v>
@@ -7090,7 +8035,7 @@
         <v>-0.07095043873136148</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1769905760956647</v>
+        <v>-0.2207990260776076</v>
       </c>
       <c r="H45" t="n">
         <v>-0.5878170628271175</v>
@@ -7108,34 +8053,34 @@
         <v>-0.2255121467360053</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.1274287907460738</v>
+        <v>-0.009900642032787128</v>
       </c>
       <c r="N45" t="n">
-        <v>0.06980722688947941</v>
+        <v>0.1043278811110261</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.1838130865281927</v>
+        <v>-0.1679141566949306</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.2919492854205141</v>
+        <v>-0.2072021205078812</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.2411493647411098</v>
+        <v>-0.2349282756511294</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.1418174353045152</v>
+        <v>-0.07483758801319154</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0605708938467228</v>
+        <v>0.0554011166548371</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.2896161150008359</v>
+        <v>-0.3134152374744904</v>
       </c>
       <c r="U45" t="n">
         <v>-0.1151507770124271</v>
       </c>
       <c r="V45" t="n">
-        <v>0.009338706958155899</v>
+        <v>0.01038027438986323</v>
       </c>
       <c r="W45" t="n">
         <v>-0.4403432846604723</v>
@@ -7147,7 +8092,7 @@
         <v>0.03827988916519637</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.1516695471769221</v>
+        <v>0.1509694371493783</v>
       </c>
       <c r="AA45" t="n">
         <v>-0.6252775130860808</v>
@@ -7177,28 +8122,28 @@
         <v>-0.1446897549316638</v>
       </c>
       <c r="AJ45" t="n">
-        <v>-0.2043179079537525</v>
+        <v>-0.284595378370627</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.2298857678683388</v>
+        <v>-0.3869703695178712</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.1933211449646071</v>
+        <v>0.2272246652718424</v>
       </c>
       <c r="AM45" t="n">
-        <v>-0.04410208223313953</v>
+        <v>-0.05178046647831222</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.03942954851506356</v>
+        <v>0.04140212172836528</v>
       </c>
       <c r="AO45" t="n">
-        <v>-0.009673963912879861</v>
+        <v>-0.01276043727367931</v>
       </c>
       <c r="AP45" t="n">
         <v>-0.01302909650925612</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.01060179377045422</v>
+        <v>0.0782271122096426</v>
       </c>
       <c r="AR45" t="n">
         <v>0.5941777483262666</v>
@@ -7213,7 +8158,28 @@
         <v>0.02857286025878127</v>
       </c>
       <c r="AV45" t="n">
-        <v>-0.509096344412644</v>
+        <v>-0.5681485701999548</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>-0.3595682771889511</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>-0.4424449254350857</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>-0.2766795722613811</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>-0.2907444253750341</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>-0.1430923289654753</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>-0.4547433202965355</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>-0.4978105744828643</v>
       </c>
     </row>
     <row r="46">
@@ -7226,7 +8192,7 @@
         <v>-0.03775376182738847</v>
       </c>
       <c r="C46" t="n">
-        <v>0.04305848750416469</v>
+        <v>0.05520830484444315</v>
       </c>
       <c r="D46" t="n">
         <v>0.1689568954546134</v>
@@ -7238,7 +8204,7 @@
         <v>0.2995102674758118</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.20476456477356</v>
+        <v>-0.2513446707483966</v>
       </c>
       <c r="H46" t="n">
         <v>-0.4919429239521828</v>
@@ -7256,34 +8222,34 @@
         <v>-0.2165905905946017</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1146187498019572</v>
+        <v>0.005024585476235494</v>
       </c>
       <c r="N46" t="n">
-        <v>0.09615487132319329</v>
+        <v>0.1186734428123374</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.1723532702135688</v>
+        <v>-0.09693078480521278</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.2574005089263018</v>
+        <v>-0.1164095296650015</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.1776081439409462</v>
+        <v>-0.1585467650561223</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.05187037608327888</v>
+        <v>0.01791400633551213</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.01190041091240638</v>
+        <v>-0.008764315562284273</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.1748545945989327</v>
+        <v>-0.1798107791738938</v>
       </c>
       <c r="U46" t="n">
         <v>-0.10039244997599</v>
       </c>
       <c r="V46" t="n">
-        <v>0.07569419017568563</v>
+        <v>0.07968229712710719</v>
       </c>
       <c r="W46" t="n">
         <v>-0.4213059024822554</v>
@@ -7295,7 +8261,7 @@
         <v>0.05464095258878708</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.06280547563647422</v>
+        <v>0.06372467345518155</v>
       </c>
       <c r="AA46" t="n">
         <v>-0.4256232770787184</v>
@@ -7325,28 +8291,28 @@
         <v>0.1729418107683882</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-0.1827806511413796</v>
+        <v>-0.2641204010536209</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.2032691755054245</v>
+        <v>-0.349175874838192</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.2580511418743375</v>
+        <v>0.2911820454334832</v>
       </c>
       <c r="AM46" t="n">
-        <v>-0.01403999438094942</v>
+        <v>-0.01181192456574095</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.09059557420830899</v>
+        <v>0.1083141243316737</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.01525382925357148</v>
+        <v>0.01455868660198485</v>
       </c>
       <c r="AP46" t="n">
         <v>0.01926137988031228</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.0290376191824257</v>
+        <v>0.04898201427126344</v>
       </c>
       <c r="AR46" t="n">
         <v>0.6898918341320829</v>
@@ -7361,7 +8327,28 @@
         <v>0.0484005527004296</v>
       </c>
       <c r="AV46" t="n">
-        <v>-0.3898082004901336</v>
+        <v>-0.3960537043463703</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>-0.2406097839137497</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>-0.4002108828812763</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>-0.1682296039286365</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>-0.1792640847100206</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>-0.1465301674357676</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>-0.2962663997811714</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>-0.1532556031726884</v>
       </c>
     </row>
     <row r="47">
@@ -7374,7 +8361,7 @@
         <v>-0.01209396018343283</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.01426140729853185</v>
+        <v>-0.02716361470761305</v>
       </c>
       <c r="D47" t="n">
         <v>0.03739136080811351</v>
@@ -7386,7 +8373,7 @@
         <v>0.04394974569248088</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.00831662258093285</v>
+        <v>-0.002286101713903709</v>
       </c>
       <c r="H47" t="n">
         <v>-0.006744813277590106</v>
@@ -7404,34 +8391,34 @@
         <v>-0.06405975867337128</v>
       </c>
       <c r="M47" t="n">
-        <v>0.01435892239391238</v>
+        <v>0.03370223779251121</v>
       </c>
       <c r="N47" t="n">
-        <v>0.03170563698488679</v>
+        <v>0.02933659984919215</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.04125819493876173</v>
+        <v>-0.01249460373696754</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.014968648018751</v>
+        <v>-0.03084446659027948</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.01360377050464844</v>
+        <v>-0.01927331603724265</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.02869991393528543</v>
+        <v>-0.01506009986054029</v>
       </c>
       <c r="S47" t="n">
-        <v>-0.02892087978229816</v>
+        <v>-0.03257881984008858</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.03652581962472267</v>
+        <v>-0.03097484195789028</v>
       </c>
       <c r="U47" t="n">
         <v>0.06704913767140704</v>
       </c>
       <c r="V47" t="n">
-        <v>-0.04652388177402114</v>
+        <v>-0.04494840410455712</v>
       </c>
       <c r="W47" t="n">
         <v>-0.01966884069152343</v>
@@ -7443,7 +8430,7 @@
         <v>-0.03601389283371469</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.03168720650065465</v>
+        <v>0.03311976038816708</v>
       </c>
       <c r="AA47" t="n">
         <v>0.002046548651976242</v>
@@ -7473,28 +8460,28 @@
         <v>-0.008895340223509464</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.02227045100925495</v>
+        <v>0.01891512641242749</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.05761936014209435</v>
+        <v>-0.06498642503756523</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.009915936955524949</v>
+        <v>0.00282136021500132</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.01864492540474369</v>
+        <v>0.009883399523441963</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.01069410600378352</v>
+        <v>0.0220374207240637</v>
       </c>
       <c r="AO47" t="n">
-        <v>-0.05968893167526011</v>
+        <v>-0.05797934533969256</v>
       </c>
       <c r="AP47" t="n">
         <v>-0.04678599694605141</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.004906262452666604</v>
+        <v>0.05655274589888924</v>
       </c>
       <c r="AR47" t="n">
         <v>0.05750015991008411</v>
@@ -7509,7 +8496,28 @@
         <v>1</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.02892258516873032</v>
+        <v>-0.03726291012022116</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>-0.03001135641563799</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0.02014366055895597</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.007462530533385437</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>-0.007759483910095706</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0.009193455519658144</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-0.03398525270815453</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0.00654659957314576</v>
       </c>
     </row>
     <row r="48">
@@ -7519,149 +8527,1353 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.209623944799484</v>
+        <v>0.1793031336837223</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2638433538714056</v>
+        <v>0.3999231830717292</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2677593139178234</v>
+        <v>-0.2860016695949006</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7909816005838053</v>
+        <v>0.8171846144867677</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.07785589404867797</v>
+        <v>-0.03686845383480093</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4726144990045736</v>
+        <v>0.4133179127442381</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6826392416562586</v>
+        <v>0.6788402517304429</v>
       </c>
       <c r="I48" t="n">
-        <v>0.01889911848241311</v>
+        <v>0.04931331923808516</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5852071991725194</v>
+        <v>0.6158037560867945</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2126071564855786</v>
+        <v>0.274542739157557</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3746962210008858</v>
+        <v>0.3574213757606134</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3864198062421532</v>
+        <v>0.2080987350435624</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.01137812145021515</v>
+        <v>-0.030360690704092</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2144791055469688</v>
+        <v>0.2082330803723523</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6135805515591946</v>
+        <v>0.3728377004587167</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.6058521846919148</v>
+        <v>0.6089550420477821</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3193338028320675</v>
+        <v>0.1807779140333277</v>
       </c>
       <c r="S48" t="n">
-        <v>-0.02560613000067955</v>
+        <v>-0.05451332587190124</v>
       </c>
       <c r="T48" t="n">
-        <v>0.7086244776126522</v>
+        <v>0.7302537651626411</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2271222331314943</v>
+        <v>0.2362241608485904</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.01684415429735896</v>
+        <v>-0.004889923139536271</v>
       </c>
       <c r="W48" t="n">
-        <v>0.5606637627484448</v>
+        <v>0.5947706649972521</v>
       </c>
       <c r="X48" t="n">
-        <v>0.2841076755947821</v>
+        <v>0.3139822242567327</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1682131543007403</v>
+        <v>0.2090434330257377</v>
       </c>
       <c r="Z48" t="n">
-        <v>-0.1359073708421409</v>
+        <v>-0.1442780016120567</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6595997207286626</v>
+        <v>0.6678933348195355</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.5337231555820273</v>
+        <v>0.53442240020944</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.4669288367515272</v>
+        <v>0.4894495451574806</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.520437605950402</v>
+        <v>0.5463621304447582</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5492467563332118</v>
+        <v>0.6048776883261389</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.6404091972583513</v>
+        <v>0.6806248726581898</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.6234314389183624</v>
+        <v>0.6508876811435927</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.2738390740062236</v>
+        <v>0.3632583210486576</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.2631907844703988</v>
+        <v>0.3567663738720898</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.3244134445681293</v>
+        <v>0.3430386514502506</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.3158562271160548</v>
+        <v>0.459947910146742</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.128577957925957</v>
+        <v>-0.2072631740152965</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.04458366533574836</v>
+        <v>0.05882693156315381</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.1114465711429114</v>
+        <v>0.1058574774407744</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.09240354949187314</v>
+        <v>0.06994885182203241</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.1154843047305477</v>
+        <v>0.07822320076903221</v>
       </c>
       <c r="AQ48" t="n">
-        <v>-0.02118957964030325</v>
+        <v>-0.06705358033225921</v>
       </c>
       <c r="AR48" t="n">
-        <v>-0.5233504175468142</v>
+        <v>-0.5872899969035876</v>
       </c>
       <c r="AS48" t="n">
-        <v>-0.509096344412644</v>
+        <v>-0.5681485701999548</v>
       </c>
       <c r="AT48" t="n">
-        <v>-0.3898082004901336</v>
+        <v>-0.3960537043463703</v>
       </c>
       <c r="AU48" t="n">
-        <v>-0.02892258516873032</v>
+        <v>-0.03726291012022116</v>
       </c>
       <c r="AV48" t="n">
         <v>1</v>
       </c>
+      <c r="AW48" t="n">
+        <v>0.8036064456349398</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0.673010683959712</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.3751688776485912</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0.576016769015445</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0.01948774803052311</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0.8433833106890897</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0.6431170910397607</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.227365919677957</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.4268482779066</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.2289060345732974</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6761087278185191</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.135366689411354</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.372667585004204</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5167563883215376</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.01403754952097144</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5666743097107507</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.3533567549098131</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2775936811620962</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.1638482024562857</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.01959990152489237</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3784424960782392</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.5650034721395143</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.7473550740999032</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.2132395132056988</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.03502082371852875</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.8672773226018615</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.1798485548765004</v>
+      </c>
+      <c r="V49" t="n">
+        <v>-0.004434693599053722</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.5782517875333385</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.2587706396305931</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.3917367993150266</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.01612089137456612</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.4947600900446236</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.6749905840460861</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.4729563532277896</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.4980210470699335</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.4465661721197558</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.5479549147472607</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.5530764767574698</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.2434353427985571</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.2392997150013057</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.2581466968643039</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.4059715509203315</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-0.1006880031145074</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.03905447760956973</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.1079028463568359</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0.1169499100107334</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.127725309968595</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>-0.06133893782327564</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>-0.3570046176139451</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>-0.3595682771889511</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>-0.2406097839137497</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>-0.03001135641563799</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0.8036064456349398</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0.6065279340271094</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0.3545928127354054</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0.6249621330392384</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0.07256012085986466</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0.8727441896345022</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0.4631871619390508</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.08312430396308478</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.2363267252924848</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.2180177782976908</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5410628268191986</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.1740323190474399</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3230216242148177</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4752771282643092</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.02685946190764365</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4795322372170178</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.1857207163260521</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2941108763826505</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.3453241012727103</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.0322267987006969</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-0.02639922454156223</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.2361928574565279</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.377944486298073</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.2691520526983202</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-0.04652141406583364</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.6069065060573356</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.5830756620007724</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.01141347698006117</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.6941971437508343</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.3935160149599109</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.2348853913906301</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.0366271227316587</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.4649874832395979</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.4602733044409125</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.3316520101674357</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.3270755937235091</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.4612545904554048</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.4835776192500575</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0.4515669914588005</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0.1772655519279273</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.1761424574103401</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.3094342677918531</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.3921734105431896</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-0.1978583971139657</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.03718859027050601</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0.0250477860796118</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0.09969766820306182</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0.09621633025239522</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>-0.0364667252430471</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>-0.5225949607345096</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>-0.4424449254350857</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>-0.4002108828812763</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0.02014366055895597</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0.673010683959712</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0.6065279340271094</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.3085662219772198</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0.471360858327992</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.1377340857438203</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0.6364036313027426</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0.3274969309175451</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.01661150843605789</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.1423863972652866</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.1113689909139462</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.3528619144563227</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.01456751283012944</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1281951899989732</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2831884714072568</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.06345874696087896</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3212853189003391</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.1969561437503825</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2093620057108942</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.05267689233523905</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.05694416337724317</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.1106053663432996</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.2399564690233986</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.205891734806674</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.1559475486800109</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.01938511865322577</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.3290769738803079</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.1246347498562098</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.01952999440031683</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.2438367338130943</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.1642293403801313</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.04579504224298886</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-0.1478385009223542</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.3167641731470777</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.1979324967648889</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.254477816945015</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.27365290254957</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.2933021784866018</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0.2280865089015486</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.2283605883235673</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0.1162303143950766</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0.1180680517956684</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.5776882800974847</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.4930561929445007</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.211331258138313</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0.09036841788404558</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0.197030409648329</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0.05868728796257727</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0.05405345453898742</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>-0.006177539529897094</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>-0.1532666451446972</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>-0.2766795722613811</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>-0.1682296039286365</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0.007462530533385437</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0.3751688776485912</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0.3545928127354054</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0.3085662219772198</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0.3043131424281587</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0.03225202155242191</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0.3792111916420067</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0.2977321636112599</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.04927282497289349</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.1921779906530965</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.1760156841180942</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5108040156227085</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.1010456772886713</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.2204074039699015</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.3975409582261368</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0004292104289614232</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.3558553253172121</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.1236750263299124</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1797252802398421</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.09814367495601811</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-0.0175707717787368</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.1060133015762211</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.2097658161201254</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.4154892501002337</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.326473181584465</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.06769849623818894</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.6708824217623492</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.1172021708350955</v>
+      </c>
+      <c r="V52" t="n">
+        <v>-0.004099908668920523</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.42280990697165</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.3061227724964301</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.04835581883999099</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-0.1065270549092127</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.3834106947106985</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.1585613980456644</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.3968093991083304</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.395016244651265</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.3450604812427399</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.3877198888288143</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.3897060692053662</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.2091196021502789</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0.1980057088920089</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.1819845225910144</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.3368805768485049</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>-0.05482950000630712</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.06108596000797413</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0.1073077198508168</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0.1097644563020201</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0.1284638226504768</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>-0.05784777492690173</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>-0.2729118244903806</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>-0.2907444253750341</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>-0.1792640847100206</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>-0.007759483910095706</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0.576016769015445</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0.6249621330392384</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0.471360858327992</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0.3043131424281587</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0.2241018678217821</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0.6661085805227036</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0.3507452462284374</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.2042643389660964</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.7642429805733403</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.2115348723672874</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1631570870208681</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.06410178871052526</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1195047354117076</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1393395701599008</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.03894180634511635</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.1221065087905358</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.03940902129475717</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.1094667207441255</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-0.07854110129772936</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-0.09035145086286839</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.06407251596811241</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0.0003645409019366314</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-0.17707275587752</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.3607781816738335</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.06387123289007536</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.1959697533576185</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-0.1040656953886713</v>
+      </c>
+      <c r="V53" t="n">
+        <v>-0.04163084610752515</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.197269666347525</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.2316487181493532</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.01839194412095833</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.04325355561788625</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.116040568176363</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.1007337830363767</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>-0.02670994797470827</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.0136598907666629</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.02336351797809936</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.01597534557079376</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-0.05284508992101768</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>-0.01847403604351073</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>-0.01614366607499205</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.01555845782064549</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.07357426170347608</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-0.04348846938485919</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>-0.03858944206792053</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>-0.04441250878897959</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>-0.02266400649411131</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>-0.01742478397602201</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>-0.085397539802953</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>-0.1216764383139707</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>-0.1430923289654753</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>-0.1465301674357676</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0.009193455519658144</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0.01948774803052311</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0.07256012085986466</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0.1377340857438203</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0.03225202155242191</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0.2241018678217821</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0.2067666331497582</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0.09111944395462646</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1979126567360726</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.3253484859825745</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.2194844033140831</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8538092432026669</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.08379329820060734</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.37859552916305</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6039132685475443</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.01994354648091521</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.5089738470469847</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.2073599623356324</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1991739737769157</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.02035448914499858</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-0.06473964903144523</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.271737946961192</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.3038552011161558</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.5546200513340656</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.4576053777797011</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.0444444381201575</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.9275227059682924</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.0599301740598937</v>
+      </c>
+      <c r="V54" t="n">
+        <v>-0.022764262734949</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.6710224830870226</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.4048143188391862</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.4094471354377904</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-0.01228966795605928</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.5734116343047393</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.7250705648714856</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.4828694250074495</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.5387442571560837</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.5043790671623233</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.5901455589024103</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0.5561646011580648</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.2846425861158252</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0.2759978438498207</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.2681256186925033</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.4547193337651752</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-0.1004272139776529</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0.03728542675149699</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.08475446203954393</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.1058103684447757</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.116973662716595</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>-0.0596143903510089</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>-0.4132590036868121</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>-0.4547433202965355</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>-0.2962663997811714</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>-0.03398525270815453</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0.8433833106890897</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0.8727441896345022</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0.6364036313027426</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0.3792111916420067</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0.6661085805227036</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0.2067666331497582</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0.6421922752980661</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.1090601958665024</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.1413963340059529</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.1403310488050334</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7562289347520853</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.58201439220482</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2328700160367897</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5018081658669395</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2671095005050831</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.4055566283116501</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.306451035316866</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2048688576506116</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.07396132103269616</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-0.03161589616811954</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.1989808435132211</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.2870130828904522</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.2825563436673188</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.1985005208538313</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-0.005657630915561502</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.4345877220985939</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.05462502801646481</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.04567458712979108</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.3220663141083442</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.1833850281156024</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.09156171134119021</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-0.204296404039238</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.532317957490831</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.311235978216522</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.308361041462254</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.363407764367706</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.3422318142793827</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.3684704204036856</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.3594044756844515</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.2513078432785797</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.245315487883977</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.205634745590387</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.2972623010005083</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>-0.06879626429771911</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0.04801291838030565</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.08126061986638175</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0.05401651248635892</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.05986019862586168</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>-0.01744565768846964</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>-0.2196935518945018</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>-0.4978105744828643</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>-0.1532556031726884</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0.00654659957314576</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0.6431170910397607</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0.4631871619390508</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0.3274969309175451</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0.2977321636112599</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0.3507452462284374</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0.09111944395462646</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0.6421922752980661</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:AV48">
+  <conditionalFormatting sqref="B2:BC55">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -7683,7 +9895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8262,6 +10474,90 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
